--- a/src/rbx/stagiaires.xlsx
+++ b/src/rbx/stagiaires.xlsx
@@ -398,12 +398,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BN55"/>
+  <dimension ref="A1:BN40"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
     <col min="5" max="5" width="36.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
@@ -412,7 +412,7 @@
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="16.83203125" customWidth="1"/>
     <col min="12" max="12" width="17.83203125" customWidth="1"/>
-    <col min="13" max="13" width="27.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
     <col min="14" max="14" width="8.83203125" customWidth="1"/>
     <col min="15" max="15" width="20.83203125" customWidth="1"/>
     <col min="16" max="16" width="5.83203125" customWidth="1"/>
@@ -422,14 +422,14 @@
     <col min="20" max="20" width="43.83203125" customWidth="1"/>
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="28.83203125" customWidth="1"/>
-    <col min="23" max="23" width="40.83203125" customWidth="1"/>
+    <col min="23" max="23" width="31.83203125" customWidth="1"/>
     <col min="24" max="24" width="13.83203125" customWidth="1"/>
     <col min="25" max="25" width="21.83203125" customWidth="1"/>
     <col min="26" max="26" width="5.83203125" customWidth="1"/>
     <col min="27" max="27" width="10.83203125" customWidth="1"/>
     <col min="28" max="28" width="5.83203125" customWidth="1"/>
     <col min="29" max="29" width="20.83203125" customWidth="1"/>
-    <col min="30" max="30" width="26.83203125" customWidth="1"/>
+    <col min="30" max="30" width="19.83203125" customWidth="1"/>
     <col min="31" max="31" width="28.83203125" customWidth="1"/>
     <col min="32" max="32" width="5.83203125" customWidth="1"/>
     <col min="33" max="33" width="6.83203125" customWidth="1"/>
@@ -448,7 +448,7 @@
     <col min="46" max="46" width="16.83203125" customWidth="1"/>
     <col min="47" max="47" width="68.83203125" customWidth="1"/>
     <col min="48" max="48" width="41.83203125" customWidth="1"/>
-    <col min="49" max="49" width="27.83203125" customWidth="1"/>
+    <col min="49" max="49" width="23.83203125" customWidth="1"/>
     <col min="50" max="50" width="68.83203125" customWidth="1"/>
     <col min="51" max="51" width="46.83203125" customWidth="1"/>
     <col min="52" max="52" width="27.83203125" customWidth="1"/>
@@ -670,22 +670,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>138799</v>
+        <v>140790</v>
       </c>
       <c r="B2" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C2" t="str">
-        <v>HEDDEBAUT</v>
+        <v xml:space="preserve">GOSSUIN </v>
       </c>
       <c r="D2" t="str">
-        <v xml:space="preserve">Irina </v>
+        <v xml:space="preserve">Lucas </v>
       </c>
       <c r="E2" t="str">
-        <v>i.heddebaut@e2c-grandlille.fr</v>
+        <v>l.gossuin@e2c-grandlille.fr</v>
       </c>
       <c r="F2" t="str">
-        <v>07.85.48.28.96</v>
+        <v>07.83.83.79.58</v>
       </c>
       <c r="G2" t="str">
         <v>Grand Lille</v>
@@ -694,31 +694,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I2" t="str">
-        <v>Vendeur / Vendeuse en boulangerie-pâtisserie, Vendeur / Vendeuse en alimentation générale</v>
+        <v>Chargé / Chargée de communication</v>
       </c>
       <c r="K2" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L2" t="str">
-        <v>référés Alexia</v>
+        <v>référés Sabah</v>
       </c>
       <c r="M2" t="str">
-        <v>2605/mai 2026 RBX</v>
+        <v>2606/juin 2026 RBX</v>
       </c>
       <c r="O2" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>SELAM Sabah</v>
       </c>
       <c r="P2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R2" s="1">
-        <v>38913</v>
+        <v>37704</v>
       </c>
       <c r="T2" t="str">
-        <v>Tourcoing</v>
+        <v xml:space="preserve">Tourcoing </v>
       </c>
       <c r="U2" t="str">
         <v>FRANCAISE</v>
@@ -726,11 +726,14 @@
       <c r="V2" t="str">
         <v>OUI</v>
       </c>
+      <c r="W2" t="str">
+        <v>49 Rue de Beaumont</v>
+      </c>
       <c r="X2" t="str">
-        <v>59166</v>
+        <v>59100</v>
       </c>
       <c r="Y2" t="str">
-        <v>Bousbecque</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z2" t="str">
         <v>Non</v>
@@ -739,10 +742,10 @@
         <v>Non</v>
       </c>
       <c r="AC2" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD2" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE2" t="str">
         <v>Non</v>
@@ -763,75 +766,78 @@
         <v>Non</v>
       </c>
       <c r="AK2" t="str">
-        <v>41h30m</v>
+        <v>80h30m</v>
       </c>
       <c r="AL2" t="str">
-        <v>0m</v>
+        <v>35h</v>
       </c>
       <c r="AM2" t="str">
         <v>3h15m</v>
       </c>
       <c r="AN2" s="1">
-        <v>46168.3918287037</v>
+        <v>46202.40107638889</v>
       </c>
       <c r="AP2" s="1">
-        <v>46444.64166666667</v>
+        <v>46475.6125</v>
       </c>
       <c r="AU2" s="1">
-        <v>46126.572916666664</v>
+        <v>46154.572916666664</v>
       </c>
       <c r="AV2" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW2" t="str">
-        <v xml:space="preserve">Messaouda </v>
+        <v>Richard SULAWA</v>
       </c>
       <c r="AX2" s="1">
-        <v>46119.646527777775</v>
+        <v>46150.686111111114</v>
       </c>
       <c r="BA2" t="str">
         <v>NON</v>
       </c>
+      <c r="BG2" t="str">
+        <v>19576</v>
+      </c>
       <c r="BH2" s="1">
-        <v>45749.083333333336</v>
+        <v>46161.083333333336</v>
       </c>
       <c r="BI2" t="str">
-        <v>10483268226</v>
+        <v>5827637N</v>
       </c>
       <c r="BJ2" t="str">
-        <v>62da7187-4bb3-4687-8ad8-a062df973790</v>
+        <v>7f397591-0680-4e49-99be-0ae48e416496</v>
       </c>
       <c r="BK2" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL2" t="str">
         <v/>
       </c>
       <c r="BM2" t="str">
-        <v>irina.heddebaut@gmail.com</v>
+        <v>lucas.gossu1@gmail.com</v>
       </c>
       <c r="BN2" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_gossuin_e2c-grandlille_fr/IgCK8zDVxchORZml3W0QRPYBAbf_vjCX6a-zNtAcopmuQLQ?e=RYvIQI</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>138790</v>
+        <v>140752</v>
       </c>
       <c r="B3" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C3" t="str">
-        <v>ISMAILI ALAOUI</v>
+        <v>CELEBI</v>
       </c>
       <c r="D3" t="str">
-        <v>Ilyes</v>
+        <v>Yasmin</v>
       </c>
       <c r="E3" t="str">
-        <v>i.ismailialaoui@e2c-grandlille.fr</v>
+        <v>y.celebi@e2c-grandlille.fr</v>
       </c>
       <c r="F3" t="str">
-        <v>07.67.56.30.85</v>
+        <v>07.67.82.62.48</v>
       </c>
       <c r="G3" t="str">
         <v>Grand Lille</v>
@@ -840,31 +846,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I3" t="str">
-        <v>Téléconseiller / Téléconseillère</v>
+        <v>Boulanger-pâtissier / Boulangère-pâtissière</v>
       </c>
       <c r="K3" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L3" t="str">
-        <v>référés David</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M3" t="str">
-        <v>2605/mai 2026 RBX</v>
+        <v>2606/juin 2026 RBX</v>
       </c>
       <c r="O3" t="str">
-        <v>KIMPE David</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R3" s="1">
-        <v>39487</v>
+        <v>38112</v>
       </c>
       <c r="T3" t="str">
-        <v>Croix</v>
+        <v xml:space="preserve">Roubaix </v>
       </c>
       <c r="U3" t="str">
         <v>FRANCAISE</v>
@@ -872,6 +878,9 @@
       <c r="V3" t="str">
         <v>OUI</v>
       </c>
+      <c r="W3" t="str">
+        <v>148 Rue d'Oran</v>
+      </c>
       <c r="X3" t="str">
         <v>59100</v>
       </c>
@@ -879,7 +888,10 @@
         <v>Roubaix</v>
       </c>
       <c r="Z3" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB3" t="str">
         <v>Non</v>
@@ -888,7 +900,7 @@
         <v>NON</v>
       </c>
       <c r="AD3" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE3" t="str">
         <v>Non</v>
@@ -909,75 +921,78 @@
         <v>Non</v>
       </c>
       <c r="AK3" t="str">
-        <v>41h30m</v>
+        <v>80h30m</v>
       </c>
       <c r="AL3" t="str">
-        <v>0m</v>
+        <v>28h</v>
       </c>
       <c r="AM3" t="str">
         <v>3h15m</v>
       </c>
       <c r="AN3" s="1">
-        <v>46168.388819444444</v>
+        <v>46202.40185185185</v>
       </c>
       <c r="AP3" s="1">
-        <v>46444.62569444445</v>
+        <v>46475.61597222222</v>
       </c>
       <c r="AU3" s="1">
-        <v>46125.572916666664</v>
+        <v>46182.572916666664</v>
       </c>
       <c r="AV3" t="str">
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW3" t="str">
-        <v xml:space="preserve">KRUG Isabelle </v>
+        <v>Isabelle KRUG</v>
       </c>
       <c r="AX3" s="1">
-        <v>46119.629166666666</v>
+        <v>46178.61111111111</v>
       </c>
       <c r="BA3" t="str">
         <v>NON</v>
       </c>
+      <c r="BG3" t="str">
+        <v>19575</v>
+      </c>
       <c r="BH3" s="1">
-        <v>46015.041666666664</v>
+        <v>46074.041666666664</v>
       </c>
       <c r="BI3" t="str">
-        <v>5970265U</v>
+        <v>5874907U</v>
       </c>
       <c r="BJ3" t="str">
-        <v>8b07fbd0-e4c3-4c2b-92a9-eeee911a2186</v>
+        <v>20cf2453-5a24-4e86-8fb0-f29eba38fde7</v>
       </c>
       <c r="BK3" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL3" t="str">
         <v/>
       </c>
       <c r="BM3" t="str">
-        <v>ilyesismail@gmail.com</v>
+        <v>yasmincelebi59@gmail.com</v>
       </c>
       <c r="BN3" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/y_celebi_e2c-grandlille_fr/IgDi5q7Fn-scSrvtAc5DLT0RAfbw1tePuiEV539gczrCNFQ?e=dKpaFg</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>138788</v>
+        <v>138799</v>
       </c>
       <c r="B4" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C4" t="str">
-        <v>MAKHLOUFI</v>
+        <v>HEDDEBAUT</v>
       </c>
       <c r="D4" t="str">
-        <v xml:space="preserve">Abdallah </v>
+        <v xml:space="preserve">Irina </v>
       </c>
       <c r="E4" t="str">
-        <v>ab.makhloufi@e2c-grandlille.fr</v>
+        <v>i.heddebaut@e2c-grandlille.fr</v>
       </c>
       <c r="F4" t="str">
-        <v>06.05.45.66.50</v>
+        <v>07.85.48.28.96</v>
       </c>
       <c r="G4" t="str">
         <v>Grand Lille</v>
@@ -986,31 +1001,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I4" t="str">
-        <v>Aide-soignant / Aide-soignante</v>
+        <v>Vendeur / Vendeuse en boulangerie-pâtisserie, Vendeur / Vendeuse en alimentation générale</v>
       </c>
       <c r="K4" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L4" t="str">
-        <v>référés Sabah</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M4" t="str">
         <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O4" t="str">
-        <v>SELAM Sabah</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R4" s="1">
-        <v>39526</v>
+        <v>38913</v>
       </c>
       <c r="T4" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v>Tourcoing</v>
       </c>
       <c r="U4" t="str">
         <v>FRANCAISE</v>
@@ -1019,10 +1034,10 @@
         <v>OUI</v>
       </c>
       <c r="X4" t="str">
-        <v>59100</v>
+        <v>59166</v>
       </c>
       <c r="Y4" t="str">
-        <v>Roubaix</v>
+        <v>Bousbecque</v>
       </c>
       <c r="Z4" t="str">
         <v>Non</v>
@@ -1055,69 +1070,81 @@
         <v>Non</v>
       </c>
       <c r="AK4" t="str">
-        <v>41h30m</v>
+        <v>155h45m</v>
       </c>
       <c r="AL4" t="str">
-        <v>0m</v>
+        <v>98h</v>
       </c>
       <c r="AM4" t="str">
-        <v>3h15m</v>
+        <v>20h30m</v>
       </c>
       <c r="AN4" s="1">
-        <v>46168.39256944445</v>
+        <v>46168.3918287037</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>46216.67847222222</v>
       </c>
       <c r="AP4" s="1">
-        <v>46444.61875</v>
+        <v>46444.64166666667</v>
       </c>
       <c r="AU4" s="1">
-        <v>46125.572916666664</v>
+        <v>46126.572916666664</v>
       </c>
       <c r="AV4" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
+        <v>En direct</v>
       </c>
       <c r="AW4" t="str">
-        <v xml:space="preserve">TATI Regina </v>
+        <v xml:space="preserve">Messaouda </v>
       </c>
       <c r="AX4" s="1">
-        <v>46119.62222222222</v>
+        <v>46119.646527777775</v>
       </c>
       <c r="BA4" t="str">
         <v>NON</v>
       </c>
+      <c r="BG4" t="str">
+        <v>17498</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>45749.083333333336</v>
+      </c>
+      <c r="BI4" t="str">
+        <v>10483268226</v>
+      </c>
       <c r="BJ4" t="str">
-        <v>7f729a56-4b8e-44f5-beef-45528fe0f197</v>
+        <v>62da7187-4bb3-4687-8ad8-a062df973790</v>
       </c>
       <c r="BK4" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL4" t="str">
         <v/>
       </c>
       <c r="BM4" t="str">
-        <v xml:space="preserve">aabdallahdz16@gmail.com </v>
+        <v>irina.heddebaut@gmail.com</v>
       </c>
       <c r="BN4" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/i_heddebaut_e2c-grandlille_fr/IgAeEBBycPokSryMywyoec0xAVJIbZ4Tp1bc4wmsPrVR6EI?e=N4HWD5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>138785</v>
+        <v>138790</v>
       </c>
       <c r="B5" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C5" t="str">
-        <v>BESSAIS</v>
+        <v>ISMAILI ALAOUI</v>
       </c>
       <c r="D5" t="str">
-        <v>Fériel</v>
+        <v>Ilyes</v>
       </c>
       <c r="E5" t="str">
-        <v>f.bessais@e2c-grandlille.fr</v>
+        <v>i.ismailialaoui@e2c-grandlille.fr</v>
       </c>
       <c r="F5" t="str">
-        <v>07.49.03.74.77</v>
+        <v>07.67.56.30.85</v>
       </c>
       <c r="G5" t="str">
         <v>Grand Lille</v>
@@ -1126,19 +1153,19 @@
         <v>Roubaix</v>
       </c>
       <c r="I5" t="str">
-        <v>Auxiliaire de vie</v>
+        <v>Téléconseiller / Téléconseillère</v>
       </c>
       <c r="K5" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L5" t="str">
-        <v>référés Sarah</v>
+        <v>référés David</v>
       </c>
       <c r="M5" t="str">
         <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O5" t="str">
-        <v>MORVAN Sarah</v>
+        <v>KIMPE David</v>
       </c>
       <c r="P5">
         <v>18</v>
@@ -1147,10 +1174,10 @@
         <v>18</v>
       </c>
       <c r="R5" s="1">
-        <v>39577</v>
+        <v>39487</v>
       </c>
       <c r="T5" t="str">
-        <v>Roubaix</v>
+        <v>Croix</v>
       </c>
       <c r="U5" t="str">
         <v>FRANCAISE</v>
@@ -1159,7 +1186,7 @@
         <v>OUI</v>
       </c>
       <c r="W5" t="str">
-        <v>53 Avenue Frasez</v>
+        <v>11 Contour Saint-Martin</v>
       </c>
       <c r="X5" t="str">
         <v>59100</v>
@@ -1180,7 +1207,7 @@
         <v>NON</v>
       </c>
       <c r="AD5" t="str">
-        <v>Infra 3</v>
+        <v>3 validé</v>
       </c>
       <c r="AE5" t="str">
         <v>Non</v>
@@ -1201,19 +1228,19 @@
         <v>Non</v>
       </c>
       <c r="AK5" t="str">
-        <v>23h45m</v>
+        <v>135h15m</v>
       </c>
       <c r="AL5" t="str">
-        <v>0m</v>
+        <v>72h</v>
       </c>
       <c r="AM5" t="str">
-        <v>19h30m</v>
+        <v>40h</v>
       </c>
       <c r="AN5" s="1">
-        <v>46168.395462962966</v>
+        <v>46168.388819444444</v>
       </c>
       <c r="AP5" s="1">
-        <v>46444.6125</v>
+        <v>46444.62569444445</v>
       </c>
       <c r="AU5" s="1">
         <v>46125.572916666664</v>
@@ -1222,54 +1249,57 @@
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW5" t="str">
-        <v>SAADA Ghemina</v>
+        <v xml:space="preserve">KRUG Isabelle </v>
       </c>
       <c r="AX5" s="1">
-        <v>46119.615277777775</v>
+        <v>46119.629166666666</v>
       </c>
       <c r="BA5" t="str">
         <v>NON</v>
       </c>
+      <c r="BG5" t="str">
+        <v>17455</v>
+      </c>
       <c r="BH5" s="1">
-        <v>46106.041666666664</v>
+        <v>46015.041666666664</v>
       </c>
       <c r="BI5" t="str">
-        <v>10519156312</v>
+        <v>5970265U</v>
       </c>
       <c r="BJ5" t="str">
-        <v>db2a91e6-0ab7-4a05-ad08-fcf32f4ae8c5</v>
+        <v>8b07fbd0-e4c3-4c2b-92a9-eeee911a2186</v>
       </c>
       <c r="BK5" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL5" t="str">
         <v/>
       </c>
       <c r="BM5" t="str">
-        <v xml:space="preserve">rielbessais0@gmail.com </v>
+        <v>ilyesismail@gmail.com</v>
       </c>
       <c r="BN5" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/i_ismailialaoui_e2c-grandlille_fr/IgB06iPyIKlXSLq3slDhWts0AT1entI9dRmwnKjbrChM-cs?e=EdNJf7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>138783</v>
+        <v>138788</v>
       </c>
       <c r="B6" t="str">
         <v>Homme</v>
       </c>
       <c r="C6" t="str">
-        <v>BARA</v>
+        <v>MAKHLOUFI</v>
       </c>
       <c r="D6" t="str">
-        <v>Jahid</v>
+        <v xml:space="preserve">Abdallah </v>
       </c>
       <c r="E6" t="str">
-        <v>j.bara@e2c-grandlille.fr</v>
+        <v>ab.makhloufi@e2c-grandlille.fr</v>
       </c>
       <c r="F6" t="str">
-        <v>07.67.23.37.05</v>
+        <v>0753985805</v>
       </c>
       <c r="G6" t="str">
         <v>Grand Lille</v>
@@ -1278,7 +1308,7 @@
         <v>Roubaix</v>
       </c>
       <c r="I6" t="str">
-        <v>Electricien / Electricienne bâtiment tertiaire</v>
+        <v>Educateur spécialisé / Educatrice spécialisée</v>
       </c>
       <c r="K6" t="str">
         <v>J'ai des idées</v>
@@ -1293,13 +1323,13 @@
         <v>SELAM Sabah</v>
       </c>
       <c r="P6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R6" s="1">
-        <v>40033</v>
+        <v>39526</v>
       </c>
       <c r="T6" t="str">
         <v xml:space="preserve">Roubaix </v>
@@ -1311,7 +1341,7 @@
         <v>OUI</v>
       </c>
       <c r="W6" t="str">
-        <v>20 Rue Kléber</v>
+        <v>292 Boulevard de Reims</v>
       </c>
       <c r="X6" t="str">
         <v>59100</v>
@@ -1332,7 +1362,7 @@
         <v>NON</v>
       </c>
       <c r="AD6" t="str">
-        <v>Infra 3</v>
+        <v>3 validé</v>
       </c>
       <c r="AE6" t="str">
         <v>Non</v>
@@ -1353,19 +1383,22 @@
         <v>Non</v>
       </c>
       <c r="AK6" t="str">
-        <v>28h30m</v>
+        <v>155h45m</v>
       </c>
       <c r="AL6" t="str">
-        <v>0m</v>
+        <v>63h</v>
       </c>
       <c r="AM6" t="str">
-        <v>16h15m</v>
+        <v>29h45m</v>
       </c>
       <c r="AN6" s="1">
-        <v>46168.396053240744</v>
+        <v>46168.39256944445</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>46216.674305555556</v>
       </c>
       <c r="AP6" s="1">
-        <v>46444.606944444444</v>
+        <v>46444.61875</v>
       </c>
       <c r="AU6" s="1">
         <v>46125.572916666664</v>
@@ -1374,63 +1407,51 @@
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW6" t="str">
-        <v xml:space="preserve">MANIEZ Marion </v>
+        <v xml:space="preserve">TATI Regina </v>
       </c>
       <c r="AX6" s="1">
-        <v>46119.60833333333</v>
+        <v>46119.62222222222</v>
       </c>
       <c r="BA6" t="str">
         <v>NON</v>
       </c>
-      <c r="BB6" t="str">
-        <v xml:space="preserve">ABROUS </v>
-      </c>
-      <c r="BC6" t="str">
-        <v>Souaide</v>
-      </c>
-      <c r="BD6" t="str">
-        <v>20 Rue Kléber 59100 Roubaix</v>
-      </c>
-      <c r="BE6" t="str">
-        <v>0767233705</v>
-      </c>
-      <c r="BF6" t="str">
-        <v>souad.ab@gmail.com</v>
+      <c r="BG6" t="str">
+        <v>17482</v>
       </c>
       <c r="BJ6" t="str">
-        <v>667b1580-0a05-4957-8e55-f0d7c447ea67</v>
+        <v>7f729a56-4b8e-44f5-beef-45528fe0f197</v>
       </c>
       <c r="BK6" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL6" t="str">
         <v/>
       </c>
       <c r="BM6" t="str">
-        <v>souad.ab@gmail.com</v>
+        <v xml:space="preserve">aabdallahdz16@gmail.com </v>
       </c>
       <c r="BN6" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/ab_makhloufi_e2c-grandlille_fr/IgDSsRkKQrlhR4D2VRq7V9OHASf2HDUZ25XG5TGOJdtSKwM?e=tV44p2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>138779</v>
+        <v>138785</v>
       </c>
       <c r="B7" t="str">
         <v>Femme</v>
       </c>
       <c r="C7" t="str">
-        <v>BETTAYEB</v>
+        <v>BESSAIS</v>
       </c>
       <c r="D7" t="str">
-        <v>Kenza</v>
+        <v>Fériel</v>
       </c>
       <c r="E7" t="str">
-        <v>k.bettayeb@e2c-grandlille.fr</v>
+        <v>f.bessais@e2c-grandlille.fr</v>
       </c>
       <c r="F7" t="str">
-        <v>07.80.60.66.17</v>
+        <v>07.49.03.74.77</v>
       </c>
       <c r="G7" t="str">
         <v>Grand Lille</v>
@@ -1438,6 +1459,9 @@
       <c r="H7" t="str">
         <v>Roubaix</v>
       </c>
+      <c r="I7" t="str">
+        <v>Auxiliaire de vie</v>
+      </c>
       <c r="K7" t="str">
         <v>J'ai des idées</v>
       </c>
@@ -1451,16 +1475,16 @@
         <v>MORVAN Sarah</v>
       </c>
       <c r="P7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R7" s="1">
-        <v>39205</v>
+        <v>39577</v>
       </c>
       <c r="T7" t="str">
-        <v>Tourcoing</v>
+        <v>Roubaix</v>
       </c>
       <c r="U7" t="str">
         <v>FRANCAISE</v>
@@ -1468,6 +1492,9 @@
       <c r="V7" t="str">
         <v>OUI</v>
       </c>
+      <c r="W7" t="str">
+        <v>53 Avenue Frasez</v>
+      </c>
       <c r="X7" t="str">
         <v>59100</v>
       </c>
@@ -1475,7 +1502,10 @@
         <v>Roubaix</v>
       </c>
       <c r="Z7" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB7" t="str">
         <v>Non</v>
@@ -1484,7 +1514,7 @@
         <v>NON</v>
       </c>
       <c r="AD7" t="str">
-        <v>3 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE7" t="str">
         <v>Non</v>
@@ -1505,19 +1535,19 @@
         <v>Non</v>
       </c>
       <c r="AK7" t="str">
-        <v>32h</v>
+        <v>105h30m</v>
       </c>
       <c r="AL7" t="str">
-        <v>0m</v>
+        <v>98h</v>
       </c>
       <c r="AM7" t="str">
-        <v>12h45m</v>
+        <v>74h30m</v>
       </c>
       <c r="AN7" s="1">
-        <v>46168.39653935185</v>
+        <v>46168.395462962966</v>
       </c>
       <c r="AP7" s="1">
-        <v>46444.60277777778</v>
+        <v>46444.6125</v>
       </c>
       <c r="AU7" s="1">
         <v>46125.572916666664</v>
@@ -1526,48 +1556,57 @@
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW7" t="str">
-        <v xml:space="preserve">KHAROUF Nagiba </v>
+        <v>SAADA Ghemina</v>
       </c>
       <c r="AX7" s="1">
-        <v>46119.60555555556</v>
+        <v>46119.615277777775</v>
       </c>
       <c r="BA7" t="str">
         <v>NON</v>
       </c>
+      <c r="BG7" t="str">
+        <v>17450</v>
+      </c>
+      <c r="BH7" s="1">
+        <v>46106.041666666664</v>
+      </c>
+      <c r="BI7" t="str">
+        <v>10519156312</v>
+      </c>
       <c r="BJ7" t="str">
-        <v>66575b84-f7ed-430d-8117-6b669d7b4a9f</v>
+        <v>db2a91e6-0ab7-4a05-ad08-fcf32f4ae8c5</v>
       </c>
       <c r="BK7" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL7" t="str">
         <v/>
       </c>
       <c r="BM7" t="str">
-        <v>kenzabettagel108@gmail.com</v>
+        <v xml:space="preserve">rielbessais0@gmail.com </v>
       </c>
       <c r="BN7" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/f_bessais_e2c-grandlille_fr/IgCYYy58l9bCRYULvfrkBaxjAa_8Exx909A2l8BayClGsJA?e=5buAa6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>138775</v>
+        <v>138783</v>
       </c>
       <c r="B8" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C8" t="str">
-        <v xml:space="preserve">CHAABANE </v>
+        <v>BARA</v>
       </c>
       <c r="D8" t="str">
-        <v>Mayssa</v>
+        <v>Jahid</v>
       </c>
       <c r="E8" t="str">
-        <v>m.chaabane@e2c-grandlille.fr</v>
+        <v>j.bara@e2c-grandlille.fr</v>
       </c>
       <c r="F8" t="str">
-        <v>06.01.55.65.61</v>
+        <v>07.67.23.37.05</v>
       </c>
       <c r="G8" t="str">
         <v>Grand Lille</v>
@@ -1576,28 +1615,28 @@
         <v>Roubaix</v>
       </c>
       <c r="I8" t="str">
-        <v>Infirmier / Infirmière en soins généraux (IDE), Installateur dépanneur / Installatrice dépanneuse en informatique</v>
+        <v>Electricien / Electricienne bâtiment tertiaire</v>
       </c>
       <c r="K8" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L8" t="str">
-        <v>référés Loic</v>
+        <v>référés Sabah</v>
       </c>
       <c r="M8" t="str">
         <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O8" t="str">
-        <v>DUCARME Loïc</v>
+        <v>SELAM Sabah</v>
       </c>
       <c r="P8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R8" s="1">
-        <v>39082</v>
+        <v>40033</v>
       </c>
       <c r="T8" t="str">
         <v xml:space="preserve">Roubaix </v>
@@ -1609,7 +1648,7 @@
         <v>OUI</v>
       </c>
       <c r="W8" t="str">
-        <v>28 Rue Beaumarchais</v>
+        <v>20 Rue Kléber</v>
       </c>
       <c r="X8" t="str">
         <v>59100</v>
@@ -1630,7 +1669,7 @@
         <v>NON</v>
       </c>
       <c r="AD8" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE8" t="str">
         <v>Non</v>
@@ -1651,19 +1690,19 @@
         <v>Non</v>
       </c>
       <c r="AK8" t="str">
-        <v>35h</v>
+        <v>121h45m</v>
       </c>
       <c r="AL8" t="str">
         <v>0m</v>
       </c>
       <c r="AM8" t="str">
-        <v>9h45m</v>
+        <v>80h30m</v>
       </c>
       <c r="AN8" s="1">
-        <v>46168.39712962963</v>
+        <v>46168.396053240744</v>
       </c>
       <c r="AP8" s="1">
-        <v>46444.592361111114</v>
+        <v>46444.606944444444</v>
       </c>
       <c r="AU8" s="1">
         <v>46125.572916666664</v>
@@ -1672,54 +1711,66 @@
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW8" t="str">
-        <v xml:space="preserve">SAADA Ghemina </v>
+        <v xml:space="preserve">MANIEZ Marion </v>
       </c>
       <c r="AX8" s="1">
-        <v>46119.59305555555</v>
+        <v>46119.60833333333</v>
       </c>
       <c r="BA8" t="str">
         <v>NON</v>
       </c>
-      <c r="BH8" s="1">
-        <v>45977.041666666664</v>
-      </c>
-      <c r="BI8" t="str">
-        <v>5854171E</v>
+      <c r="BB8" t="str">
+        <v xml:space="preserve">ABROUS </v>
+      </c>
+      <c r="BC8" t="str">
+        <v>Souaide</v>
+      </c>
+      <c r="BD8" t="str">
+        <v>20 Rue Kléber 59100 Roubaix</v>
+      </c>
+      <c r="BE8" t="str">
+        <v>0767233705</v>
+      </c>
+      <c r="BF8" t="str">
+        <v>souad.ab@gmail.com</v>
+      </c>
+      <c r="BG8" t="str">
+        <v>17459</v>
       </c>
       <c r="BJ8" t="str">
-        <v>a84a58c1-dfb8-458e-9bf3-b0dc06ac7597</v>
+        <v>667b1580-0a05-4957-8e55-f0d7c447ea67</v>
       </c>
       <c r="BK8" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL8" t="str">
         <v/>
       </c>
       <c r="BM8" t="str">
-        <v>mayssa.chaabane.mc@gmail.com</v>
+        <v>souad.ab@gmail.com</v>
       </c>
       <c r="BN8" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/j_bara_e2c-grandlille_fr/IgCBaLj4fMy2TZ-XRTR3HJu7AVrhtcLKvylE4nk4pPlZL4w?e=QmD3RP</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>138765</v>
+        <v>138779</v>
       </c>
       <c r="B9" t="str">
         <v>Femme</v>
       </c>
       <c r="C9" t="str">
-        <v>WANIN</v>
+        <v>BETTAYEB</v>
       </c>
       <c r="D9" t="str">
-        <v xml:space="preserve">Prudence </v>
+        <v>Kenza</v>
       </c>
       <c r="E9" t="str">
-        <v>p.wanin@e2c-grandlille.fr</v>
+        <v>k.bettayeb@e2c-grandlille.fr</v>
       </c>
       <c r="F9" t="str">
-        <v>06.09.48.85.91</v>
+        <v>07.80.60.66.17</v>
       </c>
       <c r="G9" t="str">
         <v>Grand Lille</v>
@@ -1727,26 +1778,29 @@
       <c r="H9" t="str">
         <v>Roubaix</v>
       </c>
+      <c r="K9" t="str">
+        <v>J'ai des idées</v>
+      </c>
       <c r="L9" t="str">
-        <v>référés Loic</v>
+        <v>référés Sarah</v>
       </c>
       <c r="M9" t="str">
         <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O9" t="str">
-        <v>DUCARME Loïc</v>
+        <v>MORVAN Sarah</v>
       </c>
       <c r="P9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R9" s="1">
-        <v>39866</v>
+        <v>39205</v>
       </c>
       <c r="T9" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v>Tourcoing</v>
       </c>
       <c r="U9" t="str">
         <v>FRANCAISE</v>
@@ -1755,16 +1809,19 @@
         <v>OUI</v>
       </c>
       <c r="W9" t="str">
-        <v>16 Rue des Mésanges</v>
+        <v>1 Rue Emile Moreau</v>
       </c>
       <c r="X9" t="str">
-        <v>59390</v>
+        <v>59100</v>
       </c>
       <c r="Y9" t="str">
-        <v>Toufflers</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z9" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB9" t="str">
         <v>Non</v>
@@ -1794,81 +1851,75 @@
         <v>Non</v>
       </c>
       <c r="AK9" t="str">
-        <v>41h30m</v>
+        <v>91h45m</v>
       </c>
       <c r="AL9" t="str">
-        <v>0m</v>
+        <v>84h45m</v>
       </c>
       <c r="AM9" t="str">
-        <v>3h15m</v>
+        <v>68h45m</v>
       </c>
       <c r="AN9" s="1">
-        <v>46168.40017361111</v>
+        <v>46168.39653935185</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>46216.59375</v>
       </c>
       <c r="AP9" s="1">
-        <v>46444.55763888889</v>
+        <v>46444.60277777778</v>
       </c>
       <c r="AU9" s="1">
-        <v>46119.572916666664</v>
+        <v>46125.572916666664</v>
       </c>
       <c r="AV9" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
+      </c>
+      <c r="AW9" t="str">
+        <v xml:space="preserve">KHAROUF Nagiba </v>
       </c>
       <c r="AX9" s="1">
-        <v>46113.56319444445</v>
+        <v>46119.60555555556</v>
       </c>
       <c r="BA9" t="str">
         <v>NON</v>
       </c>
-      <c r="BB9" t="str">
-        <v xml:space="preserve">HONQUERT </v>
-      </c>
-      <c r="BC9" t="str">
-        <v xml:space="preserve">Lise </v>
-      </c>
-      <c r="BD9" t="str">
-        <v xml:space="preserve">18 Rue des Mesanges 59390 Toufflers </v>
-      </c>
-      <c r="BE9" t="str">
-        <v xml:space="preserve">0609488591 </v>
-      </c>
-      <c r="BF9" t="str">
-        <v xml:space="preserve">prudance2202@hotmail.fr </v>
+      <c r="BG9" t="str">
+        <v>17496</v>
       </c>
       <c r="BJ9" t="str">
-        <v>d9a01719-2944-49de-969e-e26b22942a7b</v>
+        <v>66575b84-f7ed-430d-8117-6b669d7b4a9f</v>
       </c>
       <c r="BK9" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL9" t="str">
         <v/>
       </c>
       <c r="BM9" t="str">
-        <v>prudencewanin2202@gmail.com</v>
+        <v>kenzabettagel108@gmail.com</v>
       </c>
       <c r="BN9" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/k_bettayeb_e2c-grandlille_fr/IgBiEzRNzWfwSailGjNsrDuVAaG5pPIf_4Y1knOj98C9rFI?e=HbrkAo</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>138756</v>
+        <v>138775</v>
       </c>
       <c r="B10" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C10" t="str">
-        <v>ENGLIZ</v>
+        <v xml:space="preserve">CHAABANE </v>
       </c>
       <c r="D10" t="str">
-        <v>Samy</v>
+        <v>Mayssa</v>
       </c>
       <c r="E10" t="str">
-        <v>s.engliz@e2c-grandlille.fr</v>
+        <v>m.chaabane@e2c-grandlille.fr</v>
       </c>
       <c r="F10" t="str">
-        <v>06.02.45.76.72</v>
+        <v>06.01.55.65.61</v>
       </c>
       <c r="G10" t="str">
         <v>Grand Lille</v>
@@ -1877,28 +1928,28 @@
         <v>Roubaix</v>
       </c>
       <c r="I10" t="str">
-        <v>Aide-soignant / Aide-soignante, Infirmier / Infirmière en soins généraux (IDE)</v>
+        <v>Infirmier / Infirmière en soins généraux (IDE), Installateur dépanneur / Installatrice dépanneuse en informatique</v>
       </c>
       <c r="K10" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L10" t="str">
-        <v>référés Sarah</v>
+        <v>référés Loic</v>
       </c>
       <c r="M10" t="str">
         <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O10" t="str">
-        <v>MORVAN Sarah</v>
+        <v>DUCARME Loïc</v>
       </c>
       <c r="P10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R10" s="1">
-        <v>38188</v>
+        <v>39082</v>
       </c>
       <c r="T10" t="str">
         <v xml:space="preserve">Roubaix </v>
@@ -1909,6 +1960,9 @@
       <c r="V10" t="str">
         <v>OUI</v>
       </c>
+      <c r="W10" t="str">
+        <v>28 Rue Beaumarchais</v>
+      </c>
       <c r="X10" t="str">
         <v>59100</v>
       </c>
@@ -1916,7 +1970,10 @@
         <v>Roubaix</v>
       </c>
       <c r="Z10" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB10" t="str">
         <v>Non</v>
@@ -1925,7 +1982,7 @@
         <v>NON</v>
       </c>
       <c r="AD10" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE10" t="str">
         <v>Non</v>
@@ -1946,78 +2003,81 @@
         <v>Non</v>
       </c>
       <c r="AK10" t="str">
-        <v>42h45m</v>
+        <v>139h</v>
       </c>
       <c r="AL10" t="str">
-        <v>0m</v>
+        <v>75h</v>
       </c>
       <c r="AM10" t="str">
-        <v>3h15m</v>
+        <v>46h45m</v>
       </c>
       <c r="AN10" s="1">
-        <v>46168.397627314815</v>
+        <v>46168.39712962963</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>46216.4625</v>
       </c>
       <c r="AP10" s="1">
-        <v>46444.47638888889</v>
+        <v>46444.592361111114</v>
       </c>
       <c r="AU10" s="1">
-        <v>46112.572916666664</v>
+        <v>46125.572916666664</v>
       </c>
       <c r="AV10" t="str">
-        <v>POLE EMPLOI -Roubaix-</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW10" t="str">
-        <v>Lynda ENDHAMATO</v>
+        <v xml:space="preserve">SAADA Ghemina </v>
       </c>
       <c r="AX10" s="1">
-        <v>46104.479166666664</v>
-      </c>
-      <c r="AY10" t="str">
-        <v xml:space="preserve">049lynda.endhamato-masele@francetravail.net </v>
+        <v>46119.59305555555</v>
       </c>
       <c r="BA10" t="str">
         <v>NON</v>
       </c>
+      <c r="BG10" t="str">
+        <v>17446</v>
+      </c>
       <c r="BH10" s="1">
-        <v>45567.083333333336</v>
+        <v>45977.041666666664</v>
       </c>
       <c r="BI10" t="str">
-        <v>5811088A</v>
+        <v>5854171E</v>
       </c>
       <c r="BJ10" t="str">
-        <v>76e260bb-9a6f-4868-aa73-6c1d9f9ab98e</v>
+        <v>a84a58c1-dfb8-458e-9bf3-b0dc06ac7597</v>
       </c>
       <c r="BK10" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL10" t="str">
         <v/>
       </c>
       <c r="BM10" t="str">
-        <v>formationsamycom@gmail.com</v>
+        <v>mayssa.chaabane.mc@gmail.com</v>
       </c>
       <c r="BN10" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_chaabane_e2c-grandlille_fr/IgBRbwUKiXOcQafPiwZTXiuWAR1awneFG5-2pm8HKW_lKUE?e=E2K5Ap</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>135201</v>
+        <v>138765</v>
       </c>
       <c r="B11" t="str">
         <v>Femme</v>
       </c>
       <c r="C11" t="str">
-        <v>ATOUCOUMAN</v>
+        <v>WANIN</v>
       </c>
       <c r="D11" t="str">
-        <v>Anchalita</v>
+        <v xml:space="preserve">Prudence </v>
       </c>
       <c r="E11" t="str">
-        <v>a.atoucouman@e2c-grandlille.fr</v>
+        <v>p.wanin@e2c-grandlille.fr</v>
       </c>
       <c r="F11" t="str">
-        <v>0745758311</v>
+        <v>06.09.48.85.91</v>
       </c>
       <c r="G11" t="str">
         <v>Grand Lille</v>
@@ -2026,49 +2086,46 @@
         <v>Roubaix</v>
       </c>
       <c r="I11" t="str">
-        <v>Auxiliaire de vie, Assistant / Assistante de vie aux familles</v>
-      </c>
-      <c r="K11" t="str">
-        <v>J'ai des idées</v>
+        <v>Cuisinier / Cuisinière</v>
       </c>
       <c r="L11" t="str">
-        <v>référés Sarah</v>
+        <v>référés Loic</v>
       </c>
       <c r="M11" t="str">
-        <v>2604/avril 2026 RBX</v>
+        <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O11" t="str">
-        <v>MORVAN Sarah</v>
+        <v>DUCARME Loïc</v>
       </c>
       <c r="P11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R11" s="1">
-        <v>37328</v>
+        <v>39866</v>
       </c>
       <c r="T11" t="str">
-        <v>GUYANE</v>
+        <v xml:space="preserve">Roubaix </v>
       </c>
       <c r="U11" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="V11" t="str">
+        <v>OUI</v>
+      </c>
       <c r="W11" t="str">
-        <v>77 Rue Jules Guesde</v>
+        <v>16 Rue des Mésanges</v>
       </c>
       <c r="X11" t="str">
-        <v>59100</v>
+        <v>59390</v>
       </c>
       <c r="Y11" t="str">
-        <v>Roubaix</v>
+        <v>Toufflers</v>
       </c>
       <c r="Z11" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA11" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB11" t="str">
         <v>Non</v>
@@ -2098,46 +2155,55 @@
         <v>Non</v>
       </c>
       <c r="AK11" t="str">
-        <v>172h30m</v>
+        <v>121h15m</v>
       </c>
       <c r="AL11" t="str">
-        <v>0m</v>
+        <v>70h</v>
       </c>
       <c r="AM11" t="str">
-        <v>22h45m</v>
+        <v>60h15m</v>
       </c>
       <c r="AN11" s="1">
-        <v>46125.694027777776</v>
+        <v>46168.40017361111</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>46216.57777777778</v>
       </c>
       <c r="AP11" s="1">
-        <v>46400.489583333336</v>
+        <v>46444.55763888889</v>
       </c>
       <c r="AU11" s="1">
-        <v>46112.572916666664</v>
+        <v>46119.572916666664</v>
       </c>
       <c r="AV11" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
-      </c>
-      <c r="AW11" t="str">
-        <v>FABIENNE PECORTE</v>
+        <v>En direct</v>
       </c>
       <c r="AX11" s="1">
-        <v>46111.583333333336</v>
+        <v>46113.56319444445</v>
       </c>
       <c r="BA11" t="str">
         <v>NON</v>
       </c>
+      <c r="BB11" t="str">
+        <v xml:space="preserve">HONQUERT </v>
+      </c>
+      <c r="BC11" t="str">
+        <v xml:space="preserve">Lise </v>
+      </c>
+      <c r="BD11" t="str">
+        <v xml:space="preserve">18 Rue des Mesanges 59390 Toufflers </v>
+      </c>
+      <c r="BE11" t="str">
+        <v xml:space="preserve">0609488591 </v>
+      </c>
+      <c r="BF11" t="str">
+        <v xml:space="preserve">prudance2202@hotmail.fr </v>
+      </c>
       <c r="BG11" t="str">
-        <v>14683</v>
-      </c>
-      <c r="BH11" s="1">
-        <v>45993.041666666664</v>
-      </c>
-      <c r="BI11" t="str">
-        <v>5895170U</v>
+        <v>17472</v>
       </c>
       <c r="BJ11" t="str">
-        <v>9b271a13-618e-4706-a48f-4a0b0e29e028</v>
+        <v>d9a01719-2944-49de-969e-e26b22942a7b</v>
       </c>
       <c r="BK11" t="str">
         <v>Accepted</v>
@@ -2146,30 +2212,30 @@
         <v/>
       </c>
       <c r="BM11" t="str">
-        <v>pakosieangela7@gmail.com</v>
+        <v>prudencewanin2202@gmail.com</v>
       </c>
       <c r="BN11" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_atoucouman_e2c-grandlille_fr/IgD1C8QixHX4R6Mp3r14dZuyAWhKJ2nax34ork-hj67JQMw?e=4ZTZVG</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/p_wanin_e2c-grandlille_fr/IgACj-nAxpZxSqhPORxdnGerASY62j0ggDDnvcNAG3bjsf4?e=z0L8jz</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>135196</v>
+        <v>138756</v>
       </c>
       <c r="B12" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C12" t="str">
-        <v>PEREIRA</v>
+        <v>ENGLIZ</v>
       </c>
       <c r="D12" t="str">
-        <v>Clara</v>
+        <v>Samy</v>
       </c>
       <c r="E12" t="str">
-        <v>c.pereira@e2c-grandlille.fr</v>
+        <v>s.engliz@e2c-grandlille.fr</v>
       </c>
       <c r="F12" t="str">
-        <v>0651214943</v>
+        <v>06.02.45.76.72</v>
       </c>
       <c r="G12" t="str">
         <v>Grand Lille</v>
@@ -2178,7 +2244,7 @@
         <v>Roubaix</v>
       </c>
       <c r="I12" t="str">
-        <v>Masseur / Masseuse bien-être, Educateur spécialisé / Educatrice spécialisée</v>
+        <v>Aide-soignant / Aide-soignante, Infirmier / Infirmière en soins généraux (IDE)</v>
       </c>
       <c r="K12" t="str">
         <v>J'ai des idées</v>
@@ -2187,7 +2253,7 @@
         <v>référés Sarah</v>
       </c>
       <c r="M12" t="str">
-        <v>2604/avril 2026 RBX</v>
+        <v>2605/mai 2026 RBX</v>
       </c>
       <c r="O12" t="str">
         <v>MORVAN Sarah</v>
@@ -2199,10 +2265,10 @@
         <v>21</v>
       </c>
       <c r="R12" s="1">
-        <v>38136</v>
+        <v>38188</v>
       </c>
       <c r="T12" t="str">
-        <v>ROUBAIX</v>
+        <v xml:space="preserve">Roubaix </v>
       </c>
       <c r="U12" t="str">
         <v>FRANCAISE</v>
@@ -2211,7 +2277,7 @@
         <v>OUI</v>
       </c>
       <c r="W12" t="str">
-        <v>56 Rue Buffon</v>
+        <v>74 Allée des Saules</v>
       </c>
       <c r="X12" t="str">
         <v>59100</v>
@@ -2232,7 +2298,7 @@
         <v>NON</v>
       </c>
       <c r="AD12" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE12" t="str">
         <v>Non</v>
@@ -2253,46 +2319,49 @@
         <v>Non</v>
       </c>
       <c r="AK12" t="str">
-        <v>107h45m</v>
+        <v>135h30m</v>
       </c>
       <c r="AL12" t="str">
-        <v>74h30m</v>
+        <v>64h30m</v>
       </c>
       <c r="AM12" t="str">
-        <v>15h45m</v>
+        <v>49h</v>
       </c>
       <c r="AN12" s="1">
-        <v>46125.69918981481</v>
+        <v>46168.397627314815</v>
       </c>
       <c r="AP12" s="1">
-        <v>46400.479166666664</v>
+        <v>46444.47638888889</v>
       </c>
       <c r="AU12" s="1">
-        <v>46091.478472222225</v>
+        <v>46112.572916666664</v>
       </c>
       <c r="AV12" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
+        <v>POLE EMPLOI -Roubaix-</v>
       </c>
       <c r="AW12" t="str">
-        <v>MEZIANE OURIDA</v>
+        <v>Lynda ENDHAMATO</v>
       </c>
       <c r="AX12" s="1">
-        <v>46087.583333333336</v>
+        <v>46104.479166666664</v>
+      </c>
+      <c r="AY12" t="str">
+        <v xml:space="preserve">049lynda.endhamato-masele@francetravail.net </v>
       </c>
       <c r="BA12" t="str">
         <v>NON</v>
       </c>
       <c r="BG12" t="str">
-        <v>14699</v>
+        <v>17488</v>
       </c>
       <c r="BH12" s="1">
-        <v>45780.083333333336</v>
+        <v>45567.083333333336</v>
       </c>
       <c r="BI12" t="str">
-        <v>5905711B</v>
+        <v>5811088A</v>
       </c>
       <c r="BJ12" t="str">
-        <v>1375acae-87ce-408f-8128-3c488025e791</v>
+        <v>76e260bb-9a6f-4868-aa73-6c1d9f9ab98e</v>
       </c>
       <c r="BK12" t="str">
         <v>Accepted</v>
@@ -2301,30 +2370,30 @@
         <v/>
       </c>
       <c r="BM12" t="str">
-        <v>clarapereira.clara2004@gmail.com</v>
+        <v>formationsamycom@gmail.com</v>
       </c>
       <c r="BN12" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_pereira_e2c-grandlille_fr/IgBtZFroKPvWQZgMiodJlFDPAe6f_Wcku7icMTGZT_OyXRg?e=oTKmmd</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_engliz_e2c-grandlille_fr/IgDb5XqOShWiQ5QaGzZcl2KEAVKvembx3yuYiVxVhMKzdiE?e=zFb7jj</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>135191</v>
+        <v>135201</v>
       </c>
       <c r="B13" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C13" t="str">
-        <v>VERDY BEN AISSA</v>
+        <v>ATOUCOUMAN</v>
       </c>
       <c r="D13" t="str">
-        <v>Gabriel</v>
+        <v>Anchalita</v>
       </c>
       <c r="E13" t="str">
-        <v>g.verdybenaissa@e2c-grandlille.fr</v>
+        <v>a.atoucouman@e2c-grandlille.fr</v>
       </c>
       <c r="F13" t="str">
-        <v>0787567941</v>
+        <v>0745758311</v>
       </c>
       <c r="G13" t="str">
         <v>Grand Lille</v>
@@ -2333,37 +2402,37 @@
         <v>Roubaix</v>
       </c>
       <c r="I13" t="str">
-        <v>Agent administratif / Agente administrative</v>
+        <v>Auxiliaire de vie, Assistant / Assistante de vie aux familles</v>
       </c>
       <c r="K13" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L13" t="str">
-        <v>référés Loic</v>
+        <v>référés Sarah</v>
       </c>
       <c r="M13" t="str">
         <v>2604/avril 2026 RBX</v>
       </c>
       <c r="O13" t="str">
-        <v>DUCARME Loïc</v>
+        <v>MORVAN Sarah</v>
       </c>
       <c r="P13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R13" s="1">
-        <v>37919</v>
+        <v>37328</v>
       </c>
       <c r="T13" t="str">
-        <v>ROUBAIX</v>
+        <v>GUYANE</v>
       </c>
       <c r="U13" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="V13" t="str">
-        <v>OUI</v>
+      <c r="W13" t="str">
+        <v>77 Rue Jules Guesde</v>
       </c>
       <c r="X13" t="str">
         <v>59100</v>
@@ -2372,7 +2441,10 @@
         <v>Roubaix</v>
       </c>
       <c r="Z13" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB13" t="str">
         <v>Non</v>
@@ -2381,7 +2453,7 @@
         <v>NON</v>
       </c>
       <c r="AD13" t="str">
-        <v>4 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE13" t="str">
         <v>Non</v>
@@ -2402,46 +2474,49 @@
         <v>Non</v>
       </c>
       <c r="AK13" t="str">
-        <v>122h</v>
+        <v>213h15m</v>
       </c>
       <c r="AL13" t="str">
-        <v>102h30m</v>
+        <v>199h</v>
       </c>
       <c r="AM13" t="str">
-        <v>17h15m</v>
+        <v>37h</v>
       </c>
       <c r="AN13" s="1">
-        <v>46125.69993055556</v>
+        <v>46125.694027777776</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>46220.39790509259</v>
       </c>
       <c r="AP13" s="1">
-        <v>46400.46875</v>
+        <v>46400.489583333336</v>
       </c>
       <c r="AU13" s="1">
-        <v>46105.572916666664</v>
+        <v>46112.572916666664</v>
       </c>
       <c r="AV13" t="str">
-        <v>FRANCE TRAVAIL - Roubaix</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW13" t="str">
-        <v>CAMELIA GOUAIDA</v>
+        <v>FABIENNE PECORTE</v>
       </c>
       <c r="AX13" s="1">
-        <v>46097.583333333336</v>
+        <v>46111.583333333336</v>
       </c>
       <c r="BA13" t="str">
         <v>NON</v>
       </c>
       <c r="BG13" t="str">
-        <v>14692</v>
+        <v>14683</v>
       </c>
       <c r="BH13" s="1">
-        <v>45890.083333333336</v>
+        <v>45993.041666666664</v>
       </c>
       <c r="BI13" t="str">
-        <v>5837240B</v>
+        <v>5895170U</v>
       </c>
       <c r="BJ13" t="str">
-        <v>8ea01095-f3f6-4330-bf97-9ad0f55f63bd</v>
+        <v>9b271a13-618e-4706-a48f-4a0b0e29e028</v>
       </c>
       <c r="BK13" t="str">
         <v>Accepted</v>
@@ -2450,30 +2525,30 @@
         <v/>
       </c>
       <c r="BM13" t="str">
-        <v>gverdy.contact@gmail.com</v>
+        <v>pakosieangela7@gmail.com</v>
       </c>
       <c r="BN13" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/g_verdybenaissa_e2c-grandlille_fr/IgBNqlipf3mjTaBOFIIozjCqARsbJGjj3qi5f6bxEwqgIyc?e=jpbUsU</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_atoucouman_e2c-grandlille_fr/IgD1C8QixHX4R6Mp3r14dZuyAWhKJ2nax34ork-hj67JQMw?e=4ZTZVG</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>82625</v>
+        <v>135196</v>
       </c>
       <c r="B14" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C14" t="str">
-        <v>DEROO</v>
+        <v>PEREIRA</v>
       </c>
       <c r="D14" t="str">
-        <v>Ethan</v>
+        <v>Clara</v>
       </c>
       <c r="E14" t="str">
-        <v>e.deroo@e2c-grandlille.fr</v>
+        <v>c.pereira@e2c-grandlille.fr</v>
       </c>
       <c r="F14" t="str">
-        <v>0670626390</v>
+        <v>0651214943</v>
       </c>
       <c r="G14" t="str">
         <v>Grand Lille</v>
@@ -2482,31 +2557,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I14" t="str">
-        <v>Chaudronnier / Chaudronnière, Carrossier / Carrossière, Mécanicien / Mécanicienne automobile</v>
+        <v>Masseur / Masseuse bien-être, Educateur spécialisé / Educatrice spécialisée</v>
       </c>
       <c r="K14" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L14" t="str">
-        <v>référés Alexia</v>
+        <v>référés Sarah</v>
       </c>
       <c r="M14" t="str">
         <v>2604/avril 2026 RBX</v>
       </c>
       <c r="O14" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>MORVAN Sarah</v>
       </c>
       <c r="P14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R14" s="1">
-        <v>39857</v>
+        <v>38136</v>
       </c>
       <c r="T14" t="str">
-        <v>Tourcoing</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U14" t="str">
         <v>FRANCAISE</v>
@@ -2515,16 +2590,19 @@
         <v>OUI</v>
       </c>
       <c r="W14" t="str">
-        <v>41 Résidence du Château d'Eau</v>
+        <v>56 Rue Buffon</v>
       </c>
       <c r="X14" t="str">
-        <v>59960</v>
+        <v>59100</v>
       </c>
       <c r="Y14" t="str">
-        <v>Neuville-en-Ferrain</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z14" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB14" t="str">
         <v>Non</v>
@@ -2533,7 +2611,7 @@
         <v>NON</v>
       </c>
       <c r="AD14" t="str">
-        <v>3 non validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE14" t="str">
         <v>Non</v>
@@ -2554,49 +2632,49 @@
         <v>Non</v>
       </c>
       <c r="AK14" t="str">
-        <v>106h30m</v>
+        <v>181h30m</v>
       </c>
       <c r="AL14" t="str">
-        <v>105h</v>
+        <v>166h30m</v>
       </c>
       <c r="AM14" t="str">
-        <v>26h</v>
+        <v>65h30m</v>
       </c>
       <c r="AN14" s="1">
-        <v>46125.69496527778</v>
+        <v>46125.69918981481</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>46171.41111111111</v>
       </c>
       <c r="AP14" s="1">
-        <v>46400.54861111111</v>
+        <v>46400.479166666664</v>
       </c>
       <c r="AU14" s="1">
-        <v>46077.572916666664</v>
+        <v>46091.478472222225</v>
       </c>
       <c r="AV14" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
+      </c>
+      <c r="AW14" t="str">
+        <v>MEZIANE OURIDA</v>
       </c>
       <c r="AX14" s="1">
-        <v>46073.5625</v>
+        <v>46087.583333333336</v>
       </c>
       <c r="BA14" t="str">
         <v>NON</v>
       </c>
-      <c r="BB14" t="str">
-        <v>Elodie CANNIERE DEROO</v>
-      </c>
-      <c r="BD14" t="str">
-        <v>41 Résidence du Château d'eau 59960 Neuville-en-Ferrain</v>
-      </c>
-      <c r="BE14" t="str">
-        <v>0633341430</v>
-      </c>
-      <c r="BF14" t="str">
-        <v xml:space="preserve">cannierrederoo.elodie@aol.fr </v>
-      </c>
       <c r="BG14" t="str">
-        <v>14704</v>
+        <v>14699</v>
+      </c>
+      <c r="BH14" s="1">
+        <v>45780.083333333336</v>
+      </c>
+      <c r="BI14" t="str">
+        <v>5905711B</v>
       </c>
       <c r="BJ14" t="str">
-        <v>d8d44c89-2e6d-47c7-82bb-43f58b9a1446</v>
+        <v>1375acae-87ce-408f-8128-3c488025e791</v>
       </c>
       <c r="BK14" t="str">
         <v>Accepted</v>
@@ -2605,30 +2683,30 @@
         <v/>
       </c>
       <c r="BM14" t="str">
-        <v>ethanderoobs@gmail.com</v>
+        <v>clarapereira.clara2004@gmail.com</v>
       </c>
       <c r="BN14" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_deroo_e2c-grandlille_fr/IgBqVT2Tip0eQ59ZqU9lnxlrATg4UbkLH3oEtEQU8PC6RsI?e=c4vHDz</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_pereira_e2c-grandlille_fr/IgBtZFroKPvWQZgMiodJlFDPAe6f_Wcku7icMTGZT_OyXRg?e=oTKmmd</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>82620</v>
+        <v>135191</v>
       </c>
       <c r="B15" t="str">
         <v>Homme</v>
       </c>
       <c r="C15" t="str">
-        <v>FERDI</v>
+        <v>VERDY BEN AISSA</v>
       </c>
       <c r="D15" t="str">
-        <v>Jessim</v>
+        <v>Gabriel</v>
       </c>
       <c r="E15" t="str">
-        <v>j.ferdi@e2c-grandlille.fr</v>
+        <v>g.verdybenaissa@e2c-grandlille.fr</v>
       </c>
       <c r="F15" t="str">
-        <v>0625964447</v>
+        <v>0787567941</v>
       </c>
       <c r="G15" t="str">
         <v>Grand Lille</v>
@@ -2637,19 +2715,19 @@
         <v>Roubaix</v>
       </c>
       <c r="I15" t="str">
-        <v>Chargé / Chargée des relations publiques, Chargé / Chargée marketing digital</v>
+        <v>Agent administratif / Agente administrative</v>
       </c>
       <c r="K15" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L15" t="str">
-        <v>référés Alexia</v>
+        <v>référés Loic</v>
       </c>
       <c r="M15" t="str">
         <v>2604/avril 2026 RBX</v>
       </c>
       <c r="O15" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>DUCARME Loïc</v>
       </c>
       <c r="P15">
         <v>22</v>
@@ -2658,10 +2736,10 @@
         <v>22</v>
       </c>
       <c r="R15" s="1">
-        <v>38001</v>
+        <v>37919</v>
       </c>
       <c r="T15" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U15" t="str">
         <v>FRANCAISE</v>
@@ -2670,16 +2748,19 @@
         <v>OUI</v>
       </c>
       <c r="W15" t="str">
-        <v>3 Impasse Fauvarque</v>
+        <v>62 Rue Jules Watteeuw</v>
       </c>
       <c r="X15" t="str">
-        <v>59150</v>
+        <v>59100</v>
       </c>
       <c r="Y15" t="str">
-        <v>Wattrelos</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z15" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB15" t="str">
         <v>Non</v>
@@ -2709,46 +2790,49 @@
         <v>Non</v>
       </c>
       <c r="AK15" t="str">
-        <v>115h30m</v>
+        <v>213h30m</v>
       </c>
       <c r="AL15" t="str">
-        <v>98h</v>
+        <v>192h</v>
       </c>
       <c r="AM15" t="str">
-        <v>9h45m</v>
+        <v>55h45m</v>
       </c>
       <c r="AN15" s="1">
-        <v>46125.69532407408</v>
+        <v>46125.69993055556</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>46171.69097222222</v>
       </c>
       <c r="AP15" s="1">
-        <v>46400.54513888889</v>
+        <v>46400.46875</v>
       </c>
       <c r="AU15" s="1">
-        <v>46077.572916666664</v>
+        <v>46105.572916666664</v>
       </c>
       <c r="AV15" t="str">
-        <v>MISSION LOCALE WATTRELOS - LEERS</v>
+        <v>FRANCE TRAVAIL - Roubaix</v>
       </c>
       <c r="AW15" t="str">
-        <v xml:space="preserve">Sébastien MULDERMANS </v>
+        <v>CAMELIA GOUAIDA</v>
       </c>
       <c r="AX15" s="1">
-        <v>46070.59722222222</v>
-      </c>
-      <c r="AY15" t="str">
-        <v>muldermans_s@mlwattrelos.com</v>
-      </c>
-      <c r="AZ15" t="str">
-        <v>0320894433</v>
+        <v>46097.583333333336</v>
       </c>
       <c r="BA15" t="str">
         <v>NON</v>
       </c>
       <c r="BG15" t="str">
-        <v>14703</v>
+        <v>14692</v>
+      </c>
+      <c r="BH15" s="1">
+        <v>45890.083333333336</v>
+      </c>
+      <c r="BI15" t="str">
+        <v>5837240B</v>
       </c>
       <c r="BJ15" t="str">
-        <v>374801e0-fba5-4bdc-9bc5-04bff68419c4</v>
+        <v>8ea01095-f3f6-4330-bf97-9ad0f55f63bd</v>
       </c>
       <c r="BK15" t="str">
         <v>Accepted</v>
@@ -2757,30 +2841,30 @@
         <v/>
       </c>
       <c r="BM15" t="str">
-        <v>jessim.ferdi@gmail.com</v>
+        <v>gverdy.contact@gmail.com</v>
       </c>
       <c r="BN15" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/j_ferdi_e2c-grandlille_fr/IgAd8yChM9TZTKbkdnO3bLXwAa-AaQhiB0eqBOaIisBuYhE?e=GjiMIp</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/g_verdybenaissa_e2c-grandlille_fr/IgBNqlipf3mjTaBOFIIozjCqARsbJGjj3qi5f6bxEwqgIyc?e=jpbUsU</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>82565</v>
+        <v>82625</v>
       </c>
       <c r="B16" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C16" t="str">
-        <v>MAKHLOUFI</v>
+        <v>DEROO</v>
       </c>
       <c r="D16" t="str">
-        <v>Amina</v>
+        <v>Ethan</v>
       </c>
       <c r="E16" t="str">
-        <v>a.makhloufi@e2c-grandlille.fr</v>
+        <v>e.deroo@e2c-grandlille.fr</v>
       </c>
       <c r="F16" t="str">
-        <v>0605456650</v>
+        <v>0670626390</v>
       </c>
       <c r="G16" t="str">
         <v>Grand Lille</v>
@@ -2789,31 +2873,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I16" t="str">
-        <v>Auxiliaire de vie, Psychologue</v>
+        <v>Chaudronnier / Chaudronnière, Carrossier / Carrossière, Mécanicien / Mécanicienne automobile</v>
       </c>
       <c r="K16" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L16" t="str">
-        <v>référés David</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M16" t="str">
         <v>2604/avril 2026 RBX</v>
       </c>
       <c r="O16" t="str">
-        <v>KIMPE David</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P16">
         <v>17</v>
       </c>
       <c r="Q16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R16" s="1">
-        <v>39957</v>
+        <v>39857</v>
       </c>
       <c r="T16" t="str">
-        <v>Roubaix</v>
+        <v>Tourcoing</v>
       </c>
       <c r="U16" t="str">
         <v>FRANCAISE</v>
@@ -2821,11 +2905,14 @@
       <c r="V16" t="str">
         <v>OUI</v>
       </c>
+      <c r="W16" t="str">
+        <v>41 Résidence du Château d'Eau</v>
+      </c>
       <c r="X16" t="str">
-        <v>59100</v>
+        <v>59960</v>
       </c>
       <c r="Y16" t="str">
-        <v>Roubaix</v>
+        <v>Neuville-en-Ferrain</v>
       </c>
       <c r="Z16" t="str">
         <v>Non</v>
@@ -2837,7 +2924,7 @@
         <v>NON</v>
       </c>
       <c r="AD16" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE16" t="str">
         <v>Non</v>
@@ -2858,52 +2945,52 @@
         <v>Non</v>
       </c>
       <c r="AK16" t="str">
-        <v>106h15m</v>
+        <v>179h</v>
       </c>
       <c r="AL16" t="str">
-        <v>0m</v>
+        <v>150h</v>
       </c>
       <c r="AM16" t="str">
-        <v>49h45m</v>
+        <v>57h</v>
       </c>
       <c r="AN16" s="1">
-        <v>46125.69850694444</v>
+        <v>46125.69496527778</v>
+      </c>
+      <c r="AO16" s="1">
+        <v>46171.68194444444</v>
       </c>
       <c r="AP16" s="1">
-        <v>46400.54722222222</v>
+        <v>46400.54861111111</v>
       </c>
       <c r="AU16" s="1">
-        <v>46069.572916666664</v>
+        <v>46077.572916666664</v>
       </c>
       <c r="AV16" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
-      </c>
-      <c r="AW16" t="str">
-        <v>RIC ML Avec William</v>
+        <v>RESEAUX SOCIAUX</v>
       </c>
       <c r="AX16" s="1">
-        <v>46066.49375</v>
+        <v>46073.5625</v>
       </c>
       <c r="BA16" t="str">
         <v>NON</v>
       </c>
       <c r="BB16" t="str">
-        <v xml:space="preserve">MAKHLOUFI </v>
-      </c>
-      <c r="BC16" t="str">
-        <v xml:space="preserve">Sabrina </v>
+        <v>Elodie CANNIERE DEROO</v>
       </c>
       <c r="BD16" t="str">
-        <v xml:space="preserve">292/4 Boulevard de Reims 59100 Roubaix </v>
+        <v>41 Résidence du Château d'eau 59960 Neuville-en-Ferrain</v>
       </c>
       <c r="BE16" t="str">
-        <v>0605456650</v>
+        <v>0633341430</v>
+      </c>
+      <c r="BF16" t="str">
+        <v xml:space="preserve">cannierrederoo.elodie@aol.fr </v>
       </c>
       <c r="BG16" t="str">
-        <v>14696</v>
+        <v>14704</v>
       </c>
       <c r="BJ16" t="str">
-        <v>d0313b36-1344-4ddd-a682-93d487e61aaa</v>
+        <v>d8d44c89-2e6d-47c7-82bb-43f58b9a1446</v>
       </c>
       <c r="BK16" t="str">
         <v>Accepted</v>
@@ -2912,30 +2999,30 @@
         <v/>
       </c>
       <c r="BM16" t="str">
-        <v>aminamakhloufi457@gmail.com</v>
+        <v>ethanderoobs@gmail.com</v>
       </c>
       <c r="BN16" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_makhloufi_e2c-grandlille_fr/IgBfDtdPCnQsQanUh7JKQ5KOAUgXSGxhYq0XLO6sor95IAc?e=89tVVR</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_deroo_e2c-grandlille_fr/IgBqVT2Tip0eQ59ZqU9lnxlrATg4UbkLH3oEtEQU8PC6RsI?e=c4vHDz</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>82542</v>
+        <v>82620</v>
       </c>
       <c r="B17" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C17" t="str">
-        <v>MEDKOUR</v>
+        <v>FERDI</v>
       </c>
       <c r="D17" t="str">
-        <v>Nadia</v>
+        <v>Jessim</v>
       </c>
       <c r="E17" t="str">
-        <v>n.medkour@e2c-grandlille.fr</v>
+        <v>j.ferdi@e2c-grandlille.fr</v>
       </c>
       <c r="F17" t="str">
-        <v>0618918207</v>
+        <v>0625964447</v>
       </c>
       <c r="G17" t="str">
         <v>Grand Lille</v>
@@ -2944,40 +3031,46 @@
         <v>Roubaix</v>
       </c>
       <c r="I17" t="str">
-        <v>Assistant administratif / Assistante administrative</v>
+        <v>Chargé / Chargée des relations publiques, Chargé / Chargée marketing digital</v>
       </c>
       <c r="K17" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L17" t="str">
-        <v>référés David</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M17" t="str">
-        <v>2603/mars 2026 RBX</v>
+        <v>2604/avril 2026 RBX</v>
       </c>
       <c r="O17" t="str">
-        <v>KIMPE David</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R17" s="1">
-        <v>38238</v>
+        <v>38001</v>
       </c>
       <c r="T17" t="str">
-        <v xml:space="preserve">Tourcoing </v>
+        <v xml:space="preserve">Roubaix </v>
       </c>
       <c r="U17" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="V17" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="W17" t="str">
+        <v>3 Impasse Fauvarque</v>
+      </c>
       <c r="X17" t="str">
-        <v>59420</v>
+        <v>59150</v>
       </c>
       <c r="Y17" t="str">
-        <v>Mouvaux</v>
+        <v>Wattrelos</v>
       </c>
       <c r="Z17" t="str">
         <v>Non</v>
@@ -3010,43 +3103,49 @@
         <v>Non</v>
       </c>
       <c r="AK17" t="str">
-        <v>135h30m</v>
+        <v>204h45m</v>
       </c>
       <c r="AL17" t="str">
-        <v>217h30m</v>
+        <v>196h</v>
       </c>
       <c r="AM17" t="str">
-        <v>37h15m</v>
+        <v>71h30m</v>
       </c>
       <c r="AN17" s="1">
-        <v>46090.64409722222</v>
+        <v>46125.69532407408</v>
+      </c>
+      <c r="AO17" s="1">
+        <v>46171.683333333334</v>
       </c>
       <c r="AP17" s="1">
-        <v>46365.600694444445</v>
+        <v>46400.54513888889</v>
       </c>
       <c r="AU17" s="1">
-        <v>46070.572916666664</v>
+        <v>46077.572916666664</v>
       </c>
       <c r="AV17" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MISSION LOCALE WATTRELOS - LEERS</v>
+      </c>
+      <c r="AW17" t="str">
+        <v xml:space="preserve">Sébastien MULDERMANS </v>
       </c>
       <c r="AX17" s="1">
-        <v>46069.64375</v>
+        <v>46070.59722222222</v>
+      </c>
+      <c r="AY17" t="str">
+        <v>muldermans_s@mlwattrelos.com</v>
+      </c>
+      <c r="AZ17" t="str">
+        <v>0320894433</v>
       </c>
       <c r="BA17" t="str">
         <v>NON</v>
       </c>
       <c r="BG17" t="str">
-        <v>11209</v>
-      </c>
-      <c r="BH17" s="1">
-        <v>45871.083333333336</v>
-      </c>
-      <c r="BI17" t="str">
-        <v>5896112T</v>
+        <v>14703</v>
       </c>
       <c r="BJ17" t="str">
-        <v>17953830-2348-4787-bd0d-69407a2421cd</v>
+        <v>374801e0-fba5-4bdc-9bc5-04bff68419c4</v>
       </c>
       <c r="BK17" t="str">
         <v>Accepted</v>
@@ -3055,30 +3154,30 @@
         <v/>
       </c>
       <c r="BM17" t="str">
-        <v>nadia.medkour59@gmail.com</v>
+        <v>jessim.ferdi@gmail.com</v>
       </c>
       <c r="BN17" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/n_medkour_e2c-grandlille_fr/IgDW70nbforUQJKXXspABg-qAXJske9vPNCGlB1hr_SXoHs?e=YA7mPP</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/j_ferdi_e2c-grandlille_fr/IgAd8yChM9TZTKbkdnO3bLXwAa-AaQhiB0eqBOaIisBuYhE?e=GjiMIp</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>82536</v>
+        <v>82565</v>
       </c>
       <c r="B18" t="str">
         <v>Femme</v>
       </c>
       <c r="C18" t="str">
-        <v>SAFAR</v>
+        <v>MAKHLOUFI</v>
       </c>
       <c r="D18" t="str">
-        <v>Tessa</v>
+        <v>Amina</v>
       </c>
       <c r="E18" t="str">
-        <v>t.safar@e2c-grandlille.fr</v>
+        <v>a.makhloufi@e2c-grandlille.fr</v>
       </c>
       <c r="F18" t="str">
-        <v>0780702900</v>
+        <v>0605456650</v>
       </c>
       <c r="G18" t="str">
         <v>Grand Lille</v>
@@ -3087,28 +3186,28 @@
         <v>Roubaix</v>
       </c>
       <c r="I18" t="str">
-        <v>Aide-soignant / Aide-soignante</v>
+        <v>Auxiliaire de vie, Psychologue</v>
       </c>
       <c r="K18" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L18" t="str">
-        <v>référés Sabah</v>
+        <v>référés David</v>
       </c>
       <c r="M18" t="str">
-        <v>2603/mars 2026 RBX</v>
+        <v>2604/avril 2026 RBX</v>
       </c>
       <c r="O18" t="str">
-        <v>SELAM Sabah</v>
+        <v>KIMPE David</v>
       </c>
       <c r="P18">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q18">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R18" s="1">
-        <v>38236</v>
+        <v>39957</v>
       </c>
       <c r="T18" t="str">
         <v>Roubaix</v>
@@ -3120,16 +3219,19 @@
         <v>OUI</v>
       </c>
       <c r="W18" t="str">
-        <v>6 Rue Couteau</v>
+        <v>292 Boulevard de Reims</v>
       </c>
       <c r="X18" t="str">
-        <v>59150</v>
+        <v>59100</v>
       </c>
       <c r="Y18" t="str">
-        <v>Wattrelos</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z18" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB18" t="str">
         <v>Non</v>
@@ -3138,7 +3240,7 @@
         <v>NON</v>
       </c>
       <c r="AD18" t="str">
-        <v>[OLD]Niveau 3 non validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE18" t="str">
         <v>Non</v>
@@ -3159,46 +3261,55 @@
         <v>Non</v>
       </c>
       <c r="AK18" t="str">
-        <v>77h15m</v>
+        <v>189h30m</v>
       </c>
       <c r="AL18" t="str">
-        <v>0m</v>
+        <v>69h</v>
       </c>
       <c r="AM18" t="str">
-        <v>55h</v>
+        <v>90h15m</v>
       </c>
       <c r="AN18" s="1">
-        <v>46090.64444444444</v>
+        <v>46125.69850694444</v>
+      </c>
+      <c r="AO18" s="1">
+        <v>46202.620833333334</v>
       </c>
       <c r="AP18" s="1">
-        <v>46365.61736111111</v>
+        <v>46400.54722222222</v>
       </c>
       <c r="AU18" s="1">
-        <v>46070.572916666664</v>
+        <v>46069.572916666664</v>
       </c>
       <c r="AV18" t="str">
-        <v>MISSION LOCALE WATTRELOS - LEERS</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW18" t="str">
-        <v>Mathias</v>
+        <v>RIC ML Avec William</v>
       </c>
       <c r="AX18" s="1">
-        <v>46062.43819444445</v>
+        <v>46066.49375</v>
       </c>
       <c r="BA18" t="str">
         <v>NON</v>
       </c>
+      <c r="BB18" t="str">
+        <v xml:space="preserve">MAKHLOUFI </v>
+      </c>
+      <c r="BC18" t="str">
+        <v xml:space="preserve">Sabrina </v>
+      </c>
+      <c r="BD18" t="str">
+        <v xml:space="preserve">292/4 Boulevard de Reims 59100 Roubaix </v>
+      </c>
+      <c r="BE18" t="str">
+        <v>0605456650</v>
+      </c>
       <c r="BG18" t="str">
-        <v>11232</v>
-      </c>
-      <c r="BH18" s="1">
-        <v>45660.041666666664</v>
-      </c>
-      <c r="BI18" t="str">
-        <v>5604881M</v>
+        <v>14696</v>
       </c>
       <c r="BJ18" t="str">
-        <v>15dc6dcb-a4c0-4726-898f-c3e0b3dfa854</v>
+        <v>d0313b36-1344-4ddd-a682-93d487e61aaa</v>
       </c>
       <c r="BK18" t="str">
         <v>Accepted</v>
@@ -3207,30 +3318,30 @@
         <v/>
       </c>
       <c r="BM18" t="str">
-        <v>tessasafar03@icloud.com</v>
+        <v>aminamakhloufi457@gmail.com</v>
       </c>
       <c r="BN18" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_safar_e2c-grandlille_fr/IgBh5pQ8i9C_RYhtvuWJZK40AXO8aXgyuW8aNPruzaCuoAY?e=SKAIZV</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_makhloufi_e2c-grandlille_fr/IgBfDtdPCnQsQanUh7JKQ5KOAUgXSGxhYq0XLO6sor95IAc?e=89tVVR</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>82444</v>
+        <v>82542</v>
       </c>
       <c r="B19" t="str">
         <v>Femme</v>
       </c>
       <c r="C19" t="str">
-        <v>KABOUCHE</v>
+        <v>MEDKOUR</v>
       </c>
       <c r="D19" t="str">
-        <v>Lilya</v>
+        <v>Nadia</v>
       </c>
       <c r="E19" t="str">
-        <v>l.kabouche@e2c-grandlille.fr</v>
+        <v>n.medkour@e2c-grandlille.fr</v>
       </c>
       <c r="F19" t="str">
-        <v>0749183102</v>
+        <v>0618918207</v>
       </c>
       <c r="G19" t="str">
         <v>Grand Lille</v>
@@ -3239,43 +3350,43 @@
         <v>Roubaix</v>
       </c>
       <c r="I19" t="str">
-        <v>Vendeur / Vendeuse en prêt-à-porter, Employé / Employée de libre-service, Equipier polyvalent / Equipière polyvalente de restauration rapide</v>
+        <v>Assistant administratif / Assistante administrative</v>
       </c>
       <c r="K19" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L19" t="str">
-        <v>référés Alexia</v>
+        <v>référés David</v>
       </c>
       <c r="M19" t="str">
         <v>2603/mars 2026 RBX</v>
       </c>
       <c r="O19" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>KIMPE David</v>
       </c>
       <c r="P19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R19" s="1">
-        <v>40137</v>
+        <v>38238</v>
       </c>
       <c r="T19" t="str">
-        <v>Roubaix</v>
+        <v xml:space="preserve">Tourcoing </v>
       </c>
       <c r="U19" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W19" t="str">
-        <v>14 Rue Lavoisier</v>
+        <v>25 Rue Lorthiois</v>
       </c>
       <c r="X19" t="str">
-        <v>59150</v>
+        <v>59420</v>
       </c>
       <c r="Y19" t="str">
-        <v>Wattrelos</v>
+        <v>Mouvaux</v>
       </c>
       <c r="Z19" t="str">
         <v>Non</v>
@@ -3287,7 +3398,7 @@
         <v>NON</v>
       </c>
       <c r="AD19" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE19" t="str">
         <v>Non</v>
@@ -3308,46 +3419,46 @@
         <v>Non</v>
       </c>
       <c r="AK19" t="str">
-        <v>182h</v>
+        <v>199h45m</v>
       </c>
       <c r="AL19" t="str">
-        <v>182h30m</v>
+        <v>335h</v>
       </c>
       <c r="AM19" t="str">
-        <v>50h15m</v>
+        <v>110h</v>
       </c>
       <c r="AN19" s="1">
-        <v>46090.644895833335</v>
+        <v>46090.64409722222</v>
+      </c>
+      <c r="AO19" s="1">
+        <v>46136.669444444444</v>
       </c>
       <c r="AP19" s="1">
-        <v>46365.60208333333</v>
+        <v>46365.600694444445</v>
       </c>
       <c r="AU19" s="1">
-        <v>46056.572916666664</v>
+        <v>46070.572916666664</v>
       </c>
       <c r="AV19" t="str">
-        <v>MISSION LOCALE WATTRELOS - LEERS</v>
-      </c>
-      <c r="AW19" t="str">
-        <v>Paule BOUKANDOU</v>
+        <v>RESEAUX SOCIAUX</v>
       </c>
       <c r="AX19" s="1">
-        <v>46050.63680555556</v>
+        <v>46069.64375</v>
       </c>
       <c r="BA19" t="str">
         <v>NON</v>
       </c>
       <c r="BG19" t="str">
-        <v>11201</v>
+        <v>11209</v>
       </c>
       <c r="BH19" s="1">
-        <v>46041.041666666664</v>
+        <v>45871.083333333336</v>
       </c>
       <c r="BI19" t="str">
-        <v>5975698Z</v>
+        <v>5896112T</v>
       </c>
       <c r="BJ19" t="str">
-        <v>c0fff31a-8bdf-44a5-9f56-d79a04c9b5d2</v>
+        <v>17953830-2348-4787-bd0d-69407a2421cd</v>
       </c>
       <c r="BK19" t="str">
         <v>Accepted</v>
@@ -3356,10 +3467,10 @@
         <v/>
       </c>
       <c r="BM19" t="str">
-        <v>lilya.kk@icloud.com</v>
+        <v>nadia.medkour59@gmail.com</v>
       </c>
       <c r="BN19" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_kabouche_e2c-grandlille_fr/IgDkXr_COQR7T57LHNtHaiAbAY8UYHqvxF4MHXY0viYVRns?e=zyQCdl</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/n_medkour_e2c-grandlille_fr/IgDW70nbforUQJKXXspABg-qAXJske9vPNCGlB1hr_SXoHs?e=YA7mPP</v>
       </c>
     </row>
     <row r="20">
@@ -3388,7 +3499,7 @@
         <v>Roubaix</v>
       </c>
       <c r="I20" t="str">
-        <v>Agent / Agente d'accueil</v>
+        <v>Agent administratif / Agente administrative</v>
       </c>
       <c r="K20" t="str">
         <v>Je sais</v>
@@ -3463,16 +3574,19 @@
         <v>Non</v>
       </c>
       <c r="AK20" t="str">
-        <v>140h30m</v>
+        <v>217h15m</v>
       </c>
       <c r="AL20" t="str">
-        <v>214h30m</v>
+        <v>347h</v>
       </c>
       <c r="AM20" t="str">
-        <v>27h30m</v>
+        <v>63h45m</v>
       </c>
       <c r="AN20" s="1">
         <v>46090.64575231481</v>
+      </c>
+      <c r="AO20" s="1">
+        <v>46136.66527777778</v>
       </c>
       <c r="AP20" s="1">
         <v>46365.45416666667</v>
@@ -3566,6 +3680,9 @@
       <c r="R21" s="1">
         <v>38625</v>
       </c>
+      <c r="T21" t="str">
+        <v>Roubaix</v>
+      </c>
       <c r="U21" t="str">
         <v>FRANCAISE</v>
       </c>
@@ -3587,6 +3704,9 @@
       <c r="AC21" t="str">
         <v>NON</v>
       </c>
+      <c r="AD21" t="str">
+        <v>4 non validé</v>
+      </c>
       <c r="AE21" t="str">
         <v>Non</v>
       </c>
@@ -3606,16 +3726,19 @@
         <v>Non</v>
       </c>
       <c r="AK21" t="str">
-        <v>155h30m</v>
+        <v>224h</v>
       </c>
       <c r="AL21" t="str">
-        <v>134h</v>
+        <v>233h</v>
       </c>
       <c r="AM21" t="str">
-        <v>67h30m</v>
+        <v>161h30m</v>
       </c>
       <c r="AN21" s="1">
         <v>46090.64759259259</v>
+      </c>
+      <c r="AO21" s="1">
+        <v>46136.67569444444</v>
       </c>
       <c r="AP21" s="1">
         <v>46365.62430555555</v>
@@ -3659,22 +3782,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>82382</v>
+        <v>82379</v>
       </c>
       <c r="B22" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C22" t="str">
-        <v>OUELBANI</v>
+        <v>PEREIRA</v>
       </c>
       <c r="D22" t="str">
-        <v>Mathis</v>
+        <v xml:space="preserve"> Léa</v>
       </c>
       <c r="E22" t="str">
-        <v>m.ouelbani@e2c-grandlille.fr</v>
+        <v>l.pereira@e2c-grandlille.fr</v>
       </c>
       <c r="F22" t="str">
-        <v>0759975333</v>
+        <v>0641462261</v>
       </c>
       <c r="G22" t="str">
         <v>Grand Lille</v>
@@ -3683,31 +3806,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I22" t="str">
-        <v>Maçon / Maçonne</v>
+        <v>Hôte / Hôtesse de caisse services clients</v>
       </c>
       <c r="K22" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L22" t="str">
-        <v>référés Alexia</v>
+        <v>référés Sabah</v>
       </c>
       <c r="M22" t="str">
-        <v>2603/mars 2026 RBX</v>
+        <v>2606/juin 2026 RBX</v>
       </c>
       <c r="O22" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>SELAM Sabah</v>
       </c>
       <c r="P22">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q22">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R22" s="1">
-        <v>39199</v>
+        <v>37079</v>
       </c>
       <c r="T22" t="str">
-        <v>Lille</v>
+        <v>Roubaix</v>
       </c>
       <c r="U22" t="str">
         <v>FRANCAISE</v>
@@ -3715,15 +3838,6 @@
       <c r="V22" t="str">
         <v>OUI</v>
       </c>
-      <c r="W22" t="str">
-        <v>51 Rue Antoine Watteau</v>
-      </c>
-      <c r="X22" t="str">
-        <v>59493</v>
-      </c>
-      <c r="Y22" t="str">
-        <v>Villeneuve-d'Ascq</v>
-      </c>
       <c r="Z22" t="str">
         <v>Non</v>
       </c>
@@ -3734,7 +3848,7 @@
         <v>NON</v>
       </c>
       <c r="AD22" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE22" t="str">
         <v>Non</v>
@@ -3755,52 +3869,52 @@
         <v>Non</v>
       </c>
       <c r="AK22" t="str">
-        <v>111h</v>
+        <v>74h</v>
       </c>
       <c r="AL22" t="str">
-        <v>0m</v>
+        <v>35h</v>
       </c>
       <c r="AM22" t="str">
-        <v>75h15m</v>
+        <v>9h45m</v>
       </c>
       <c r="AN22" s="1">
-        <v>46090.64912037037</v>
+        <v>46202.40231481481</v>
       </c>
       <c r="AP22" s="1">
-        <v>46365.6</v>
+        <v>46475.61041666667</v>
       </c>
       <c r="AU22" s="1">
         <v>46049.572916666664</v>
       </c>
       <c r="AV22" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW22" t="str">
-        <v>Mathilde RULANCE (ADELIE)</v>
+        <v>Grégory SCHOONOOGHE</v>
       </c>
       <c r="AX22" s="1">
-        <v>46062.64861111111</v>
+        <v>46043.68263888889</v>
       </c>
       <c r="AY22" t="str">
-        <v>mrulence@adelie-vamb.fr</v>
+        <v xml:space="preserve">gschoonooghe@oseroubaix.fr </v>
       </c>
       <c r="AZ22" t="str">
-        <v>0320710000</v>
+        <v>0362260400</v>
       </c>
       <c r="BA22" t="str">
         <v>NON</v>
       </c>
       <c r="BG22" t="str">
-        <v>11220</v>
+        <v>19579</v>
       </c>
       <c r="BH22" s="1">
-        <v>45804.083333333336</v>
+        <v>46174.083333333336</v>
       </c>
       <c r="BI22" t="str">
-        <v>5859103R</v>
+        <v>5500696T</v>
       </c>
       <c r="BJ22" t="str">
-        <v>54f2d413-9bb3-40fa-bba7-401c618ab4fc</v>
+        <v>e46b57ff-d4f0-45d8-9eb9-bffee8ffa136</v>
       </c>
       <c r="BK22" t="str">
         <v>Accepted</v>
@@ -3809,10 +3923,10 @@
         <v/>
       </c>
       <c r="BM22" t="str">
-        <v>u2869555325@gmail.com</v>
+        <v>leapereira59150@gmail.com</v>
       </c>
       <c r="BN22" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_ouelbani_e2c-grandlille_fr/IgCcpDffL-dXT5_me2uFuO3PAckUTlivrLhwvDQOqP0EUDY?e=Ubsesh</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_pereira_e2c-grandlille_fr/IgASXwwJcH-QRqRB_CG0XbvtAV7ypJmv4PEley478-tMvqk?e=0EcKIB</v>
       </c>
     </row>
     <row r="23">
@@ -3892,7 +4006,7 @@
         <v>NON</v>
       </c>
       <c r="AD23" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE23" t="str">
         <v>Non</v>
@@ -3913,13 +4027,13 @@
         <v>Non</v>
       </c>
       <c r="AK23" t="str">
-        <v>28h45m</v>
+        <v>98h15m</v>
       </c>
       <c r="AL23" t="str">
-        <v>0m</v>
+        <v>26h</v>
       </c>
       <c r="AM23" t="str">
-        <v>16h</v>
+        <v>78h45m</v>
       </c>
       <c r="AN23" s="1">
         <v>46168.3981712963</v>
@@ -3949,16 +4063,19 @@
         <v>21 rue de Rohan 59100 Roubaix</v>
       </c>
       <c r="BE23" t="str">
-        <v>0748300982</v>
+        <v>0748386304</v>
       </c>
       <c r="BF23" t="str">
         <v>inaa.md5911@icloud.com</v>
       </c>
+      <c r="BG23" t="str">
+        <v>17466</v>
+      </c>
       <c r="BJ23" t="str">
         <v>023d9a44-6e0e-45d3-933a-87f5a1a76163</v>
       </c>
       <c r="BK23" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL23" t="str">
         <v/>
@@ -3967,7 +4084,7 @@
         <v>l.verstraete@gmail.com</v>
       </c>
       <c r="BN23" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_verstraete_e2c-grandlille_fr/IgDhLuj9CbUYR7ulc2UqS2w3Aba-c1ffCEq9fhNLXnakG90?e=HP50BE</v>
       </c>
     </row>
     <row r="24">
@@ -3996,7 +4113,7 @@
         <v>Roubaix</v>
       </c>
       <c r="I24" t="str">
-        <v>Animateur sportif / Animatrice sportive</v>
+        <v>Animateur sportif / Animatrice sportive, Agent / Agente de sécurité</v>
       </c>
       <c r="K24" t="str">
         <v>J'explore</v>
@@ -4071,16 +4188,19 @@
         <v>Non</v>
       </c>
       <c r="AK24" t="str">
-        <v>176h45m</v>
+        <v>241h30m</v>
       </c>
       <c r="AL24" t="str">
-        <v>164h</v>
+        <v>238h</v>
       </c>
       <c r="AM24" t="str">
-        <v>132h</v>
+        <v>222h15m</v>
       </c>
       <c r="AN24" s="1">
         <v>46055.66133101852</v>
+      </c>
+      <c r="AO24" s="1">
+        <v>46104.490277777775</v>
       </c>
       <c r="AP24" s="1">
         <v>46328.69375</v>
@@ -4127,22 +4247,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>78676</v>
+        <v>78672</v>
       </c>
       <c r="B25" t="str">
         <v>Femme</v>
       </c>
       <c r="C25" t="str">
-        <v>TAVARES</v>
+        <v>AIT YOUSSEF</v>
       </c>
       <c r="D25" t="str">
-        <v>Lesly</v>
+        <v>Nawel</v>
       </c>
       <c r="E25" t="str">
-        <v>l.tavares@e2c-grandlille.fr</v>
+        <v>n.aityoussef@e2c-grandlille.fr</v>
       </c>
       <c r="F25" t="str">
-        <v>0765873252</v>
+        <v>0699565341</v>
       </c>
       <c r="G25" t="str">
         <v>Grand Lille</v>
@@ -4151,31 +4271,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I25" t="str">
-        <v>Prothésiste ongulaire, Psychologue</v>
+        <v>Préparateur / Préparatrice en pharmacie</v>
       </c>
       <c r="K25" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L25" t="str">
-        <v>référés Sabah</v>
+        <v>référés Loic</v>
       </c>
       <c r="M25" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O25" t="str">
-        <v>SELAM Sabah</v>
+        <v>DUCARME Loïc</v>
       </c>
       <c r="P25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R25" s="1">
-        <v>38555</v>
+        <v>38341</v>
       </c>
       <c r="T25" t="str">
-        <v>Tourcoing</v>
+        <v xml:space="preserve">Roubaix </v>
       </c>
       <c r="U25" t="str">
         <v>FRANCAISE</v>
@@ -4184,7 +4304,7 @@
         <v>OUI</v>
       </c>
       <c r="W25" t="str">
-        <v>7 Rue de Mons</v>
+        <v>15 Rue d'Isly</v>
       </c>
       <c r="X25" t="str">
         <v>59100</v>
@@ -4226,37 +4346,49 @@
         <v>Non</v>
       </c>
       <c r="AK25" t="str">
-        <v>209h45m</v>
+        <v>378h</v>
       </c>
       <c r="AL25" t="str">
-        <v>169h</v>
+        <v>239h</v>
       </c>
       <c r="AM25" t="str">
-        <v>47h</v>
+        <v>72h45m</v>
       </c>
       <c r="AN25" s="1">
-        <v>46055.6621875</v>
+        <v>46055.66504629629</v>
+      </c>
+      <c r="AO25" s="1">
+        <v>46182.67056712963</v>
       </c>
       <c r="AP25" s="1">
-        <v>46328.694444444445</v>
+        <v>46328.697916666664</v>
       </c>
       <c r="AU25" s="1">
-        <v>46031.479166666664</v>
+        <v>46006.604166666664</v>
       </c>
       <c r="AV25" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
+      </c>
+      <c r="AW25" t="str">
+        <v>Negiba KHAROUF</v>
       </c>
       <c r="AX25" s="1">
-        <v>46031.91111111111</v>
+        <v>46006.788194444445</v>
       </c>
       <c r="BA25" t="str">
         <v>NON</v>
       </c>
       <c r="BG25" t="str">
-        <v>10064</v>
+        <v>10055</v>
+      </c>
+      <c r="BH25" s="1">
+        <v>45952.083333333336</v>
+      </c>
+      <c r="BI25" t="str">
+        <v>10495531143</v>
       </c>
       <c r="BJ25" t="str">
-        <v>cef2485e-198f-46a0-b442-faec4fdda3df</v>
+        <v>c97df10d-6c6b-4148-bdac-0ce4f6a0cfd6</v>
       </c>
       <c r="BK25" t="str">
         <v>Accepted</v>
@@ -4273,22 +4405,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>78675</v>
+        <v>78671</v>
       </c>
       <c r="B26" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C26" t="str">
-        <v>CASTANET</v>
+        <v>WANEGUE</v>
       </c>
       <c r="D26" t="str">
-        <v>Jéssy</v>
+        <v>Emeline</v>
       </c>
       <c r="E26" t="str">
-        <v>j.castanet@e2c-grandlille.fr</v>
+        <v>e.wanegue@e2c-grandlille.fr</v>
       </c>
       <c r="F26" t="str">
-        <v>0746264483</v>
+        <v>06 17 94 54 33</v>
       </c>
       <c r="G26" t="str">
         <v>Grand Lille</v>
@@ -4296,29 +4428,32 @@
       <c r="H26" t="str">
         <v>Roubaix</v>
       </c>
+      <c r="I26" t="str">
+        <v>Infirmier / Infirmière en soins généraux (IDE)</v>
+      </c>
       <c r="K26" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L26" t="str">
-        <v>référés Sabah</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M26" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O26" t="str">
-        <v>SELAM Sabah</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R26" s="1">
-        <v>38135</v>
+        <v>38860</v>
       </c>
       <c r="T26" t="str">
-        <v>Grand-Bourg</v>
+        <v>Croix</v>
       </c>
       <c r="U26" t="str">
         <v>FRANCAISE</v>
@@ -4327,19 +4462,16 @@
         <v>OUI</v>
       </c>
       <c r="W26" t="str">
-        <v>81 Rue des Poutrains</v>
+        <v>98 Rue Philibert Delorme</v>
       </c>
       <c r="X26" t="str">
-        <v>59200</v>
+        <v>59100</v>
       </c>
       <c r="Y26" t="str">
-        <v>Tourcoing</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z26" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA26" t="str">
-        <v>QN05983M</v>
+        <v>Non</v>
       </c>
       <c r="AB26" t="str">
         <v>Non</v>
@@ -4348,7 +4480,7 @@
         <v>NON</v>
       </c>
       <c r="AD26" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE26" t="str">
         <v>Non</v>
@@ -4357,7 +4489,7 @@
         <v>Non</v>
       </c>
       <c r="AG26" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH26" t="str">
         <v>Non</v>
@@ -4369,43 +4501,46 @@
         <v>Non</v>
       </c>
       <c r="AK26" t="str">
-        <v>188h45m</v>
+        <v>197h</v>
       </c>
       <c r="AL26" t="str">
-        <v>129h</v>
+        <v>111h30m</v>
       </c>
       <c r="AM26" t="str">
-        <v>126h30m</v>
+        <v>181h30m</v>
       </c>
       <c r="AN26" s="1">
-        <v>46055.6631712963</v>
+        <v>46055.66577546296</v>
+      </c>
+      <c r="AO26" s="1">
+        <v>46104.654861111114</v>
       </c>
       <c r="AP26" s="1">
-        <v>46328.69513888889</v>
+        <v>46328.705555555556</v>
       </c>
       <c r="AU26" s="1">
-        <v>46031.4375</v>
+        <v>46027.65972222222</v>
       </c>
       <c r="AV26" t="str">
-        <v>MELT MISSION EMPLOI LYS TOURCOING</v>
+        <v>FRANCE TRAVAIL - Roubaix</v>
       </c>
       <c r="AX26" s="1">
-        <v>46031.90555555555</v>
+        <v>46027.78333333333</v>
       </c>
       <c r="BA26" t="str">
         <v>NON</v>
       </c>
       <c r="BG26" t="str">
-        <v>10062</v>
+        <v>10053</v>
       </c>
       <c r="BH26" s="1">
-        <v>45939.083333333336</v>
+        <v>45917.083333333336</v>
       </c>
       <c r="BI26" t="str">
-        <v>5951205B</v>
+        <v>5942331F</v>
       </c>
       <c r="BJ26" t="str">
-        <v>6f68c127-61fc-4fac-8660-e2807889ec54</v>
+        <v>e51b3137-1361-425f-9819-6acac16318db</v>
       </c>
       <c r="BK26" t="str">
         <v>Accepted</v>
@@ -4422,22 +4557,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>78672</v>
+        <v>78670</v>
       </c>
       <c r="B27" t="str">
         <v>Femme</v>
       </c>
       <c r="C27" t="str">
-        <v>AIT YOUSSEF</v>
+        <v>COTTENIER</v>
       </c>
       <c r="D27" t="str">
-        <v>Nawel</v>
+        <v>Clara</v>
       </c>
       <c r="E27" t="str">
-        <v>n.aityoussef@e2c-grandlille.fr</v>
+        <v>c.cottenier@e2c-grandlille.fr</v>
       </c>
       <c r="F27" t="str">
-        <v>0699565341</v>
+        <v>0749631921</v>
       </c>
       <c r="G27" t="str">
         <v>Grand Lille</v>
@@ -4446,31 +4581,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I27" t="str">
-        <v>Préparateur / Préparatrice en pharmacie</v>
+        <v>Auxiliaire de vie</v>
       </c>
       <c r="K27" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L27" t="str">
-        <v>référés Loic</v>
+        <v>référés Sarah</v>
       </c>
       <c r="M27" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O27" t="str">
-        <v>DUCARME Loïc</v>
+        <v>MORVAN Sarah</v>
       </c>
       <c r="P27">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q27">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R27" s="1">
-        <v>38341</v>
+        <v>39867</v>
       </c>
       <c r="T27" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v xml:space="preserve">Armentières </v>
       </c>
       <c r="U27" t="str">
         <v>FRANCAISE</v>
@@ -4479,19 +4614,16 @@
         <v>OUI</v>
       </c>
       <c r="W27" t="str">
-        <v>15 Rue d'Isly</v>
+        <v>69 Rue de Dunkerque</v>
       </c>
       <c r="X27" t="str">
-        <v>59100</v>
+        <v>59200</v>
       </c>
       <c r="Y27" t="str">
-        <v>Roubaix</v>
+        <v>Tourcoing</v>
       </c>
       <c r="Z27" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA27" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB27" t="str">
         <v>Non</v>
@@ -4500,7 +4632,7 @@
         <v>NON</v>
       </c>
       <c r="AD27" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE27" t="str">
         <v>Non</v>
@@ -4521,46 +4653,43 @@
         <v>Non</v>
       </c>
       <c r="AK27" t="str">
-        <v>283h30m</v>
+        <v>206h45m</v>
       </c>
       <c r="AL27" t="str">
-        <v>197h</v>
+        <v>125h30m</v>
       </c>
       <c r="AM27" t="str">
-        <v>26h</v>
+        <v>203h15m</v>
       </c>
       <c r="AN27" s="1">
-        <v>46055.66504629629</v>
+        <v>46055.66599537037</v>
+      </c>
+      <c r="AO27" s="1">
+        <v>46104.36944444444</v>
       </c>
       <c r="AP27" s="1">
-        <v>46328.697916666664</v>
+        <v>46328.37291666667</v>
       </c>
       <c r="AU27" s="1">
-        <v>46006.604166666664</v>
+        <v>46027.4375</v>
       </c>
       <c r="AV27" t="str">
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW27" t="str">
-        <v>Negiba KHAROUF</v>
+        <v>Jérémy</v>
       </c>
       <c r="AX27" s="1">
-        <v>46006.788194444445</v>
+        <v>46027.77916666667</v>
       </c>
       <c r="BA27" t="str">
         <v>NON</v>
       </c>
       <c r="BG27" t="str">
-        <v>10055</v>
-      </c>
-      <c r="BH27" s="1">
-        <v>45952.083333333336</v>
-      </c>
-      <c r="BI27" t="str">
-        <v>10495531143</v>
+        <v>10052</v>
       </c>
       <c r="BJ27" t="str">
-        <v>c97df10d-6c6b-4148-bdac-0ce4f6a0cfd6</v>
+        <v>cc318b50-9482-4ddd-b6a6-f08d86ffa4b3</v>
       </c>
       <c r="BK27" t="str">
         <v>Accepted</v>
@@ -4577,22 +4706,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>78671</v>
+        <v>78669</v>
       </c>
       <c r="B28" t="str">
         <v>Femme</v>
       </c>
       <c r="C28" t="str">
-        <v>WANEGUE</v>
+        <v>BOUTHORS</v>
       </c>
       <c r="D28" t="str">
-        <v>Emeline</v>
+        <v>Maelys</v>
       </c>
       <c r="E28" t="str">
-        <v>e.wanegue@e2c-grandlille.fr</v>
+        <v>m.bouthors@e2c-grandlille.fr</v>
       </c>
       <c r="F28" t="str">
-        <v>06179455433</v>
+        <v>0698951741</v>
       </c>
       <c r="G28" t="str">
         <v>Grand Lille</v>
@@ -4601,31 +4730,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I28" t="str">
-        <v>Infirmier / Infirmière en soins généraux (IDE)</v>
+        <v>Assistant / Assistante ressources humaines</v>
       </c>
       <c r="K28" t="str">
-        <v>J'ai des idées</v>
+        <v>J'y vais</v>
       </c>
       <c r="L28" t="str">
-        <v>référés Alexia</v>
+        <v>référés Rosetta</v>
       </c>
       <c r="M28" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O28" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>COLACCINO Rosetta</v>
       </c>
       <c r="P28">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q28">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R28" s="1">
-        <v>38860</v>
+        <v>39366</v>
       </c>
       <c r="T28" t="str">
-        <v>Croix</v>
+        <v>Villeneuve d'Ascq</v>
       </c>
       <c r="U28" t="str">
         <v>FRANCAISE</v>
@@ -4634,13 +4763,13 @@
         <v>OUI</v>
       </c>
       <c r="W28" t="str">
-        <v>98 Rue Philibert Delorme</v>
+        <v>143 Rue du Général Leclerc</v>
       </c>
       <c r="X28" t="str">
-        <v>59100</v>
+        <v>59390</v>
       </c>
       <c r="Y28" t="str">
-        <v>Roubaix</v>
+        <v>Lys-lez-Lannoy</v>
       </c>
       <c r="Z28" t="str">
         <v>Non</v>
@@ -4661,7 +4790,7 @@
         <v>Non</v>
       </c>
       <c r="AG28" t="str">
-        <v>AVEC</v>
+        <v>SANS</v>
       </c>
       <c r="AH28" t="str">
         <v>Non</v>
@@ -4673,43 +4802,40 @@
         <v>Non</v>
       </c>
       <c r="AK28" t="str">
-        <v>161h15m</v>
+        <v>350h15m</v>
       </c>
       <c r="AL28" t="str">
-        <v>84h30m</v>
+        <v>318h30m</v>
       </c>
       <c r="AM28" t="str">
-        <v>138h15m</v>
+        <v>71h45m</v>
       </c>
       <c r="AN28" s="1">
-        <v>46055.66577546296</v>
+        <v>46055.66641203704</v>
+      </c>
+      <c r="AO28" s="1">
+        <v>46104.69305555556</v>
       </c>
       <c r="AP28" s="1">
-        <v>46328.705555555556</v>
+        <v>46328.69375</v>
       </c>
       <c r="AU28" s="1">
-        <v>46027.65972222222</v>
+        <v>46027.61111111111</v>
       </c>
       <c r="AV28" t="str">
-        <v>FRANCE TRAVAIL - Roubaix</v>
+        <v>RESEAUX SOCIAUX</v>
       </c>
       <c r="AX28" s="1">
-        <v>46027.78333333333</v>
+        <v>46027.770833333336</v>
       </c>
       <c r="BA28" t="str">
         <v>NON</v>
       </c>
       <c r="BG28" t="str">
-        <v>10053</v>
-      </c>
-      <c r="BH28" s="1">
-        <v>45917.083333333336</v>
-      </c>
-      <c r="BI28" t="str">
-        <v>5942331F</v>
+        <v>10051</v>
       </c>
       <c r="BJ28" t="str">
-        <v>e51b3137-1361-425f-9819-6acac16318db</v>
+        <v>5ac7ce38-adb1-4131-aeb4-a7770c7ecd87</v>
       </c>
       <c r="BK28" t="str">
         <v>Accepted</v>
@@ -4726,22 +4852,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>78670</v>
+        <v>78668</v>
       </c>
       <c r="B29" t="str">
         <v>Femme</v>
       </c>
       <c r="C29" t="str">
-        <v>COTTENIER</v>
+        <v>VAN SLAMBROUCK</v>
       </c>
       <c r="D29" t="str">
-        <v>Clara</v>
+        <v>Thiffany</v>
       </c>
       <c r="E29" t="str">
-        <v>c.cottenier@e2c-grandlille.fr</v>
+        <v>t.vanslambrouck@e2c-grandlille.fr</v>
       </c>
       <c r="F29" t="str">
-        <v>0749631921</v>
+        <v>0612543105</v>
       </c>
       <c r="G29" t="str">
         <v>Grand Lille</v>
@@ -4750,31 +4876,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I29" t="str">
-        <v>Auxiliaire de vie</v>
+        <v>Auxiliaire de puériculture</v>
       </c>
       <c r="K29" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L29" t="str">
-        <v>référés Sarah</v>
+        <v>référés David</v>
       </c>
       <c r="M29" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O29" t="str">
-        <v>MORVAN Sarah</v>
+        <v>KIMPE David</v>
       </c>
       <c r="P29">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q29">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="R29" s="1">
-        <v>39867</v>
+        <v>37415</v>
       </c>
       <c r="T29" t="str">
-        <v xml:space="preserve">Armentières </v>
+        <v>Tourcoing</v>
       </c>
       <c r="U29" t="str">
         <v>FRANCAISE</v>
@@ -4783,7 +4909,7 @@
         <v>OUI</v>
       </c>
       <c r="W29" t="str">
-        <v>69 Rue de Dunkerque</v>
+        <v>30 Rue des Girondins</v>
       </c>
       <c r="X29" t="str">
         <v>59200</v>
@@ -4792,7 +4918,10 @@
         <v>Tourcoing</v>
       </c>
       <c r="Z29" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA29" t="str">
+        <v>QN05983M</v>
       </c>
       <c r="AB29" t="str">
         <v>Non</v>
@@ -4801,7 +4930,7 @@
         <v>NON</v>
       </c>
       <c r="AD29" t="str">
-        <v>[OLD]Niveau 3 non validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE29" t="str">
         <v>Non</v>
@@ -4822,37 +4951,40 @@
         <v>Non</v>
       </c>
       <c r="AK29" t="str">
-        <v>176h</v>
+        <v>312h45m</v>
       </c>
       <c r="AL29" t="str">
-        <v>208h30m</v>
+        <v>453h30m</v>
       </c>
       <c r="AM29" t="str">
-        <v>143h30m</v>
+        <v>35h</v>
       </c>
       <c r="AN29" s="1">
-        <v>46055.66599537037</v>
+        <v>46055.66675925926</v>
+      </c>
+      <c r="AO29" s="1">
+        <v>46104.64791666667</v>
+      </c>
+      <c r="AP29" s="1">
+        <v>46328.64791666667</v>
       </c>
       <c r="AU29" s="1">
-        <v>46027.4375</v>
+        <v>46027.583333333336</v>
       </c>
       <c r="AV29" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
-      </c>
-      <c r="AW29" t="str">
-        <v>Jérémy</v>
+        <v>RESEAUX SOCIAUX</v>
       </c>
       <c r="AX29" s="1">
-        <v>46027.77916666667</v>
+        <v>46027.76527777778</v>
       </c>
       <c r="BA29" t="str">
         <v>NON</v>
       </c>
       <c r="BG29" t="str">
-        <v>10052</v>
+        <v>10048</v>
       </c>
       <c r="BJ29" t="str">
-        <v>cc318b50-9482-4ddd-b6a6-f08d86ffa4b3</v>
+        <v>07c444cc-107d-4026-a1e7-46212f986300</v>
       </c>
       <c r="BK29" t="str">
         <v>Accepted</v>
@@ -4869,22 +5001,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>78669</v>
+        <v>78553</v>
       </c>
       <c r="B30" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C30" t="str">
-        <v>BOUTHORS</v>
+        <v>MBIYAVANGA ZOLA</v>
       </c>
       <c r="D30" t="str">
-        <v>Maelys</v>
+        <v>Jérémy</v>
       </c>
       <c r="E30" t="str">
-        <v>m.bouthors@e2c-grandlille.fr</v>
+        <v>j.mbiyavangazola@e2c-grandlille.fr</v>
       </c>
       <c r="F30" t="str">
-        <v>0698951741</v>
+        <v>0778106047</v>
       </c>
       <c r="G30" t="str">
         <v>Grand Lille</v>
@@ -4892,32 +5024,29 @@
       <c r="H30" t="str">
         <v>Roubaix</v>
       </c>
-      <c r="I30" t="str">
-        <v>Assistant / Assistante ressources humaines</v>
-      </c>
       <c r="K30" t="str">
-        <v>J'y vais</v>
+        <v>J'explore</v>
       </c>
       <c r="L30" t="str">
-        <v>référés Rosetta</v>
+        <v>référés David</v>
       </c>
       <c r="M30" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O30" t="str">
-        <v>COLACCINO Rosetta</v>
+        <v>KIMPE David</v>
       </c>
       <c r="P30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R30" s="1">
-        <v>39366</v>
+        <v>38466</v>
       </c>
       <c r="T30" t="str">
-        <v>Villeneuve d'Ascq</v>
+        <v xml:space="preserve">Lille </v>
       </c>
       <c r="U30" t="str">
         <v>FRANCAISE</v>
@@ -4926,13 +5055,13 @@
         <v>OUI</v>
       </c>
       <c r="W30" t="str">
-        <v>143 Rue du Général Leclerc</v>
+        <v>25 Rue Soufflot</v>
       </c>
       <c r="X30" t="str">
-        <v>59390</v>
+        <v>59200</v>
       </c>
       <c r="Y30" t="str">
-        <v>Lys-lez-Lannoy</v>
+        <v>Tourcoing</v>
       </c>
       <c r="Z30" t="str">
         <v>Non</v>
@@ -4965,34 +5094,40 @@
         <v>Non</v>
       </c>
       <c r="AK30" t="str">
-        <v>294h30m</v>
+        <v>202h15m</v>
       </c>
       <c r="AL30" t="str">
-        <v>214h30m</v>
+        <v>194h</v>
       </c>
       <c r="AM30" t="str">
-        <v>25h30m</v>
+        <v>254h15m</v>
       </c>
       <c r="AN30" s="1">
-        <v>46055.66641203704</v>
+        <v>46055.66427083333</v>
+      </c>
+      <c r="AO30" s="1">
+        <v>46139.49722222222</v>
+      </c>
+      <c r="AP30" s="1">
+        <v>46328.49791666667</v>
       </c>
       <c r="AU30" s="1">
-        <v>46027.61111111111</v>
+        <v>46034.70972222222</v>
       </c>
       <c r="AV30" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>FRANCE TRAVAIL - Roubaix</v>
       </c>
       <c r="AX30" s="1">
-        <v>46027.770833333336</v>
+        <v>46027.771527777775</v>
       </c>
       <c r="BA30" t="str">
         <v>NON</v>
       </c>
       <c r="BG30" t="str">
-        <v>10051</v>
+        <v>10058</v>
       </c>
       <c r="BJ30" t="str">
-        <v>5ac7ce38-adb1-4131-aeb4-a7770c7ecd87</v>
+        <v>9e4c326e-faf6-4235-90f0-73e5e5e93500</v>
       </c>
       <c r="BK30" t="str">
         <v>Accepted</v>
@@ -5009,22 +5144,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>78668</v>
+        <v>77902</v>
       </c>
       <c r="B31" t="str">
         <v>Femme</v>
       </c>
       <c r="C31" t="str">
-        <v>VAN SLAMBROUCK</v>
+        <v>SART</v>
       </c>
       <c r="D31" t="str">
-        <v>Thiffany</v>
+        <v>Manon</v>
       </c>
       <c r="E31" t="str">
-        <v>t.vanslambrouck@e2c-grandlille.fr</v>
+        <v>m.sart@e2c-grandlille.fr</v>
       </c>
       <c r="F31" t="str">
-        <v>0612543105</v>
+        <v>07 86 13 58 87</v>
       </c>
       <c r="G31" t="str">
         <v>Grand Lille</v>
@@ -5033,31 +5168,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I31" t="str">
-        <v>Auxiliaire de puériculture</v>
+        <v>Agent spécialisé / Agente spécialisée des écoles maternelles (ASEM), Animateur / Animatrice jeunesse, Educateur / Educatrice de jeunes enfants</v>
       </c>
       <c r="K31" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L31" t="str">
-        <v>référés David</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M31" t="str">
         <v>2602/février 2026 RBX</v>
       </c>
       <c r="O31" t="str">
-        <v>KIMPE David</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P31">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q31">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R31" s="1">
-        <v>37415</v>
+        <v>38807</v>
       </c>
       <c r="T31" t="str">
-        <v>Tourcoing</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U31" t="str">
         <v>FRANCAISE</v>
@@ -5066,28 +5201,28 @@
         <v>OUI</v>
       </c>
       <c r="W31" t="str">
-        <v>30 Rue des Girondins</v>
+        <v>34 Rue Henri Dunant</v>
       </c>
       <c r="X31" t="str">
-        <v>59200</v>
+        <v>59100</v>
       </c>
       <c r="Y31" t="str">
-        <v>Tourcoing</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z31" t="str">
         <v>Oui</v>
       </c>
       <c r="AA31" t="str">
-        <v>QN05983M</v>
+        <v>QN05980M</v>
       </c>
       <c r="AB31" t="str">
         <v>Non</v>
       </c>
       <c r="AC31" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD31" t="str">
-        <v>4 non validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE31" t="str">
         <v>Non</v>
@@ -5102,40 +5237,55 @@
         <v>Non</v>
       </c>
       <c r="AI31" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AJ31" t="str">
         <v>Non</v>
       </c>
       <c r="AK31" t="str">
-        <v>199h15m</v>
+        <v>273h45m</v>
       </c>
       <c r="AL31" t="str">
-        <v>328h30m</v>
+        <v>241h30m</v>
       </c>
       <c r="AM31" t="str">
-        <v>30h45m</v>
+        <v>92h</v>
       </c>
       <c r="AN31" s="1">
-        <v>46055.66675925926</v>
+        <v>46051.8853125</v>
+      </c>
+      <c r="AO31" s="1">
+        <v>46104.5</v>
+      </c>
+      <c r="AP31" s="1">
+        <v>46328.5</v>
       </c>
       <c r="AU31" s="1">
-        <v>46027.583333333336</v>
+        <v>46028.629166666666</v>
       </c>
       <c r="AV31" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
+      </c>
+      <c r="AW31" t="str">
+        <v>Nedjoy NARINUTH</v>
       </c>
       <c r="AX31" s="1">
-        <v>46027.76527777778</v>
+        <v>46006.74722222222</v>
+      </c>
+      <c r="AY31" t="str">
+        <v>narinuth.n@mlroubaix.com</v>
+      </c>
+      <c r="AZ31" t="str">
+        <v>0761544579</v>
       </c>
       <c r="BA31" t="str">
         <v>NON</v>
       </c>
       <c r="BG31" t="str">
-        <v>10048</v>
+        <v>10046</v>
       </c>
       <c r="BJ31" t="str">
-        <v>07c444cc-107d-4026-a1e7-46212f986300</v>
+        <v>781f436b-dedf-45ca-9486-550a85b03548</v>
       </c>
       <c r="BK31" t="str">
         <v>Accepted</v>
@@ -5152,22 +5302,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>78553</v>
+        <v>76175</v>
       </c>
       <c r="B32" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C32" t="str">
-        <v>MBIYAVANGA ZOLA</v>
+        <v>DEBOIS-CAZEAUD</v>
       </c>
       <c r="D32" t="str">
-        <v>Jérémy</v>
+        <v>Coline</v>
       </c>
       <c r="E32" t="str">
-        <v>j.mbiyavangazola@e2c-grandlille.fr</v>
+        <v>c.debois-cazeaud@e2c-grandlille.fr</v>
       </c>
       <c r="F32" t="str">
-        <v>0778106047</v>
+        <v>0695539587</v>
       </c>
       <c r="G32" t="str">
         <v>Grand Lille</v>
@@ -5175,17 +5325,20 @@
       <c r="H32" t="str">
         <v>Roubaix</v>
       </c>
+      <c r="I32" t="str">
+        <v>Assistant maternel / Assistante maternelle</v>
+      </c>
       <c r="K32" t="str">
-        <v>J'explore</v>
+        <v>Je sais</v>
       </c>
       <c r="L32" t="str">
-        <v>référés David</v>
+        <v>référés Sarah</v>
       </c>
       <c r="M32" t="str">
-        <v>2602/février 2026 RBX</v>
+        <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O32" t="str">
-        <v>KIMPE David</v>
+        <v>MORVAN Sarah</v>
       </c>
       <c r="P32">
         <v>21</v>
@@ -5194,10 +5347,13 @@
         <v>20</v>
       </c>
       <c r="R32" s="1">
-        <v>38466</v>
+        <v>38428</v>
+      </c>
+      <c r="S32" t="str">
+        <v>DEBOIS-CAZEAUD</v>
       </c>
       <c r="T32" t="str">
-        <v xml:space="preserve">Lille </v>
+        <v>Lille</v>
       </c>
       <c r="U32" t="str">
         <v>FRANCAISE</v>
@@ -5206,7 +5362,7 @@
         <v>OUI</v>
       </c>
       <c r="W32" t="str">
-        <v>25 Rue Soufflot</v>
+        <v>46 Rue d'Alger</v>
       </c>
       <c r="X32" t="str">
         <v>59200</v>
@@ -5224,7 +5380,7 @@
         <v>NON</v>
       </c>
       <c r="AD32" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE32" t="str">
         <v>Non</v>
@@ -5245,34 +5401,40 @@
         <v>Non</v>
       </c>
       <c r="AK32" t="str">
-        <v>130h</v>
+        <v>347h15m</v>
       </c>
       <c r="AL32" t="str">
-        <v>157h</v>
+        <v>233h40m</v>
       </c>
       <c r="AM32" t="str">
-        <v>180h15m</v>
+        <v>140h25m</v>
       </c>
       <c r="AN32" s="1">
-        <v>46055.66427083333</v>
+        <v>46035.57876157408</v>
+      </c>
+      <c r="AO32" s="1">
+        <v>46080.49166666667</v>
+      </c>
+      <c r="AP32" s="1">
+        <v>46307.495833333334</v>
       </c>
       <c r="AU32" s="1">
-        <v>46034.70972222222</v>
+        <v>45996.61875</v>
       </c>
       <c r="AV32" t="str">
-        <v>FRANCE TRAVAIL - Roubaix</v>
+        <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AX32" s="1">
-        <v>46027.771527777775</v>
+        <v>45995.62013888889</v>
       </c>
       <c r="BA32" t="str">
         <v>NON</v>
       </c>
       <c r="BG32" t="str">
-        <v>10058</v>
+        <v>9430</v>
       </c>
       <c r="BJ32" t="str">
-        <v>9e4c326e-faf6-4235-90f0-73e5e5e93500</v>
+        <v>e835cf4d-cb57-477d-802d-946ac7ffe39c</v>
       </c>
       <c r="BK32" t="str">
         <v>Accepted</v>
@@ -5284,27 +5446,27 @@
         <v/>
       </c>
       <c r="BN32" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_debois-cazeaud_e2c-grandlille_fr/IgBkCTbUU3rQT7B_S_aqTRu2AQpzHQ_-90gzWD7pabRZaWs?e=GOnsys</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>78544</v>
+        <v>76162</v>
       </c>
       <c r="B33" t="str">
         <v>Homme</v>
       </c>
       <c r="C33" t="str">
-        <v>SIMEON</v>
+        <v>DJEMOUI</v>
       </c>
       <c r="D33" t="str">
-        <v>Mathias</v>
+        <v>Liham</v>
       </c>
       <c r="E33" t="str">
-        <v>m.simeon@e2c-grandlille.fr</v>
+        <v>l.djemoui@e2c-grandlille.fr</v>
       </c>
       <c r="F33" t="str">
-        <v>0766674361</v>
+        <v>0766931926</v>
       </c>
       <c r="G33" t="str">
         <v>Grand Lille</v>
@@ -5313,28 +5475,28 @@
         <v>Roubaix</v>
       </c>
       <c r="I33" t="str">
-        <v>Agent / Agente de nettoyage en collectivité, Agent / Agente de propreté et d'hygiène, Agent / Agente de propreté de locaux</v>
+        <v>Animateur / Animatrice d'activités audiovisuelles, Organisateur / Organisatrice d'activités événementielles, Animateur socioéducatif / Animatrice socioéducative</v>
       </c>
       <c r="K33" t="str">
-        <v>J'y vais</v>
+        <v>Je sais</v>
       </c>
       <c r="L33" t="str">
         <v>référés Alexia</v>
       </c>
       <c r="M33" t="str">
-        <v>2602/février 2026 RBX</v>
+        <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O33" t="str">
         <v>ARNAUD Alexia</v>
       </c>
       <c r="P33">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q33">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R33" s="1">
-        <v>37183</v>
+        <v>38818</v>
       </c>
       <c r="T33" t="str">
         <v>Roubaix</v>
@@ -5346,19 +5508,16 @@
         <v>OUI</v>
       </c>
       <c r="W33" t="str">
-        <v>80 Rue Decrême</v>
+        <v>137 Rue du Vieux Bureau</v>
       </c>
       <c r="X33" t="str">
-        <v>59100</v>
+        <v>59150</v>
       </c>
       <c r="Y33" t="str">
-        <v>Roubaix</v>
+        <v>Wattrelos</v>
       </c>
       <c r="Z33" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA33" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB33" t="str">
         <v>Non</v>
@@ -5388,66 +5547,72 @@
         <v>Non</v>
       </c>
       <c r="AK33" t="str">
-        <v>213h15m</v>
+        <v>292h45m</v>
       </c>
       <c r="AL33" t="str">
-        <v>187h</v>
+        <v>270h</v>
       </c>
       <c r="AM33" t="str">
-        <v>64h30m</v>
+        <v>173h15m</v>
       </c>
       <c r="AN33" s="1">
-        <v>46055.664826388886</v>
+        <v>46035.58021990741</v>
+      </c>
+      <c r="AO33" s="1">
+        <v>46080.49791666667</v>
+      </c>
+      <c r="AP33" s="1">
+        <v>46307.49791666667</v>
       </c>
       <c r="AU33" s="1">
-        <v>46042.67916666667</v>
+        <v>46000.606944444444</v>
       </c>
       <c r="AV33" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MISSION LOCALE WATTRELOS - LEERS</v>
       </c>
       <c r="AX33" s="1">
-        <v>46034.75902777778</v>
+        <v>45999.60902777778</v>
       </c>
       <c r="BA33" t="str">
         <v>NON</v>
       </c>
       <c r="BG33" t="str">
-        <v>10056</v>
+        <v>9460</v>
       </c>
       <c r="BJ33" t="str">
-        <v>77613348-22f1-4218-9b33-cf2fe1b7fffd</v>
+        <v>24438f74-6789-4524-b70a-4879fa29d9a1</v>
       </c>
       <c r="BK33" t="str">
         <v>Accepted</v>
       </c>
       <c r="BL33" t="str">
-        <v/>
+        <v>18/03/26 : J'ai des idées &gt; je sais : Audiovisuelle/Évenementie</v>
       </c>
       <c r="BM33" t="str">
         <v/>
       </c>
       <c r="BN33" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/personal/l_djemoui_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fl%5Fdjemoui%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FE2C&amp;ga=1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>77902</v>
+        <v>76109</v>
       </c>
       <c r="B34" t="str">
         <v>Femme</v>
       </c>
       <c r="C34" t="str">
-        <v>SART</v>
+        <v>SINNAEVE</v>
       </c>
       <c r="D34" t="str">
-        <v>Manon</v>
+        <v>Ambre</v>
       </c>
       <c r="E34" t="str">
-        <v>m.sart@e2c-grandlille.fr</v>
+        <v>a.sinnaeve@e2c-grandlille.fr</v>
       </c>
       <c r="F34" t="str">
-        <v>07 86 13 58 87</v>
+        <v>0786814938</v>
       </c>
       <c r="G34" t="str">
         <v>Grand Lille</v>
@@ -5456,19 +5621,19 @@
         <v>Roubaix</v>
       </c>
       <c r="I34" t="str">
-        <v>Agent spécialisé / Agente spécialisée des écoles maternelles (ASEM), Animateur / Animatrice jeunesse, Educateur / Educatrice de jeunes enfants</v>
+        <v>Moniteur éducateur / Monitrice éducatrice</v>
       </c>
       <c r="K34" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L34" t="str">
-        <v>référés Alexia</v>
+        <v>référés David</v>
       </c>
       <c r="M34" t="str">
-        <v>2602/février 2026 RBX</v>
+        <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O34" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>KIMPE David</v>
       </c>
       <c r="P34">
         <v>20</v>
@@ -5477,10 +5642,13 @@
         <v>19</v>
       </c>
       <c r="R34" s="1">
-        <v>38807</v>
+        <v>38839</v>
+      </c>
+      <c r="S34" t="str">
+        <v>SINNAEVE</v>
       </c>
       <c r="T34" t="str">
-        <v>ROUBAIX</v>
+        <v xml:space="preserve">Roubaix </v>
       </c>
       <c r="U34" t="str">
         <v>FRANCAISE</v>
@@ -5489,28 +5657,25 @@
         <v>OUI</v>
       </c>
       <c r="W34" t="str">
-        <v>34 Rue Henri Dunant</v>
+        <v>23 Rue la Fontaine</v>
       </c>
       <c r="X34" t="str">
-        <v>59100</v>
+        <v>59250</v>
       </c>
       <c r="Y34" t="str">
-        <v>Roubaix</v>
+        <v>Halluin</v>
       </c>
       <c r="Z34" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA34" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB34" t="str">
         <v>Non</v>
       </c>
       <c r="AC34" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD34" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE34" t="str">
         <v>Non</v>
@@ -5525,49 +5690,49 @@
         <v>Non</v>
       </c>
       <c r="AI34" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AJ34" t="str">
         <v>Non</v>
       </c>
       <c r="AK34" t="str">
-        <v>211h30m</v>
+        <v>212h15m</v>
       </c>
       <c r="AL34" t="str">
-        <v>209h</v>
+        <v>206h</v>
       </c>
       <c r="AM34" t="str">
-        <v>66h15m</v>
+        <v>198h15m</v>
       </c>
       <c r="AN34" s="1">
-        <v>46051.8853125</v>
+        <v>46035.60104166667</v>
+      </c>
+      <c r="AO34" s="1">
+        <v>46080.66805555556</v>
+      </c>
+      <c r="AP34" s="1">
+        <v>46307.669444444444</v>
       </c>
       <c r="AU34" s="1">
-        <v>46028.629166666666</v>
+        <v>45974.48055555556</v>
       </c>
       <c r="AV34" t="str">
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AW34" t="str">
-        <v>Nedjoy NARINUTH</v>
+        <v>M. GRACA Marques</v>
       </c>
       <c r="AX34" s="1">
-        <v>46006.74722222222</v>
-      </c>
-      <c r="AY34" t="str">
-        <v>narinuth.n@mlroubaix.com</v>
-      </c>
-      <c r="AZ34" t="str">
-        <v>0761544579</v>
+        <v>45971.48611111111</v>
       </c>
       <c r="BA34" t="str">
         <v>NON</v>
       </c>
       <c r="BG34" t="str">
-        <v>10046</v>
+        <v>9419</v>
       </c>
       <c r="BJ34" t="str">
-        <v>781f436b-dedf-45ca-9486-550a85b03548</v>
+        <v>286b045d-d9f4-429a-8036-4fa8cf6d9c28</v>
       </c>
       <c r="BK34" t="str">
         <v>Accepted</v>
@@ -5584,22 +5749,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>76175</v>
+        <v>57232</v>
       </c>
       <c r="B35" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C35" t="str">
-        <v>DEBOIS-CAZEAUD</v>
+        <v>MEZIANI</v>
       </c>
       <c r="D35" t="str">
-        <v>Coline</v>
+        <v>Ilian</v>
       </c>
       <c r="E35" t="str">
-        <v>c.debois-cazeaud@e2c-grandlille.fr</v>
+        <v>i.meziani@e2c-grandlille.fr</v>
       </c>
       <c r="F35" t="str">
-        <v>0695539587</v>
+        <v>0614790289</v>
       </c>
       <c r="G35" t="str">
         <v>Grand Lille</v>
@@ -5608,52 +5773,49 @@
         <v>Roubaix</v>
       </c>
       <c r="I35" t="str">
-        <v>Assistant maternel / Assistante maternelle</v>
+        <v>Animateur / Animatrice d'activités audiovisuelles, Assistant monteur / Assistante monteuse audiovisuel, Vendeur / Vendeuse en boulangerie-pâtisserie</v>
       </c>
       <c r="K35" t="str">
-        <v>Je sais</v>
+        <v>J'explore</v>
       </c>
       <c r="L35" t="str">
-        <v>référés Sarah</v>
+        <v>référés Alexia</v>
       </c>
       <c r="M35" t="str">
         <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O35" t="str">
-        <v>MORVAN Sarah</v>
+        <v>ARNAUD Alexia</v>
       </c>
       <c r="P35">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q35">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R35" s="1">
-        <v>38428</v>
-      </c>
-      <c r="S35" t="str">
-        <v>DEBOIS-CAZEAUD</v>
+        <v>39163</v>
       </c>
       <c r="T35" t="str">
-        <v>Lille</v>
+        <v>TOURCOING, FRANCE</v>
       </c>
       <c r="U35" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="V35" t="str">
-        <v>OUI</v>
-      </c>
       <c r="W35" t="str">
-        <v>46 Rue d'Alger</v>
+        <v>12 12 Rue Fromé</v>
       </c>
       <c r="X35" t="str">
-        <v>59200</v>
+        <v>59100</v>
       </c>
       <c r="Y35" t="str">
-        <v>Tourcoing</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="Z35" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA35" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB35" t="str">
         <v>Non</v>
@@ -5662,7 +5824,7 @@
         <v>NON</v>
       </c>
       <c r="AD35" t="str">
-        <v>3 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE35" t="str">
         <v>Non</v>
@@ -5683,34 +5845,40 @@
         <v>Non</v>
       </c>
       <c r="AK35" t="str">
-        <v>256h15m</v>
+        <v>265h45m</v>
       </c>
       <c r="AL35" t="str">
-        <v>176h40m</v>
+        <v>238h</v>
       </c>
       <c r="AM35" t="str">
-        <v>94h25m</v>
+        <v>198h</v>
       </c>
       <c r="AN35" s="1">
-        <v>46035.57876157408</v>
+        <v>46035.599710648145</v>
+      </c>
+      <c r="AO35" s="1">
+        <v>46101.65833333333</v>
+      </c>
+      <c r="AP35" s="1">
+        <v>46307.65902777778</v>
       </c>
       <c r="AU35" s="1">
-        <v>45996.61875</v>
+        <v>45988</v>
       </c>
       <c r="AV35" t="str">
         <v>MISSION LOCALE DE ROUBAIX</v>
       </c>
       <c r="AX35" s="1">
-        <v>45995.62013888889</v>
+        <v>45986</v>
       </c>
       <c r="BA35" t="str">
         <v>NON</v>
       </c>
       <c r="BG35" t="str">
-        <v>9430</v>
+        <v>9452</v>
       </c>
       <c r="BJ35" t="str">
-        <v>e835cf4d-cb57-477d-802d-946ac7ffe39c</v>
+        <v>8ea45b31-b6de-4d0d-86de-c2886c002a2a</v>
       </c>
       <c r="BK35" t="str">
         <v>Accepted</v>
@@ -5727,22 +5895,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>76162</v>
+        <v>56266</v>
       </c>
       <c r="B36" t="str">
         <v>Homme</v>
       </c>
       <c r="C36" t="str">
-        <v>DJEMOUI</v>
+        <v>DOUDJEDID</v>
       </c>
       <c r="D36" t="str">
-        <v>Liham</v>
+        <v>Amayes</v>
       </c>
       <c r="E36" t="str">
-        <v>l.djemoui@e2c-grandlille.fr</v>
+        <v>a.doudjedid@e2c-grandlille.fr</v>
       </c>
       <c r="F36" t="str">
-        <v>0766931926</v>
+        <v>0745840498</v>
       </c>
       <c r="G36" t="str">
         <v>Grand Lille</v>
@@ -5751,49 +5919,52 @@
         <v>Roubaix</v>
       </c>
       <c r="I36" t="str">
-        <v>Animateur / Animatrice d'activités audiovisuelles, Organisateur / Organisatrice d'activités événementielles, Animateur socioéducatif / Animatrice socioéducative</v>
+        <v>Aide-soignant / Aide-soignante, Éducateur / Éducatrice de jeunes enfants</v>
       </c>
       <c r="K36" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L36" t="str">
-        <v>référés Alexia</v>
+        <v>référés Sabah</v>
       </c>
       <c r="M36" t="str">
         <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O36" t="str">
-        <v>ARNAUD Alexia</v>
+        <v>SELAM Sabah</v>
       </c>
       <c r="P36">
+        <v>21</v>
+      </c>
+      <c r="Q36">
         <v>20</v>
       </c>
-      <c r="Q36">
-        <v>19</v>
-      </c>
       <c r="R36" s="1">
-        <v>38818</v>
+        <v>38463</v>
       </c>
       <c r="T36" t="str">
-        <v>Roubaix</v>
+        <v>ROUBAIX, FRANCE</v>
       </c>
       <c r="U36" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V36" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="W36" t="str">
-        <v>137 Rue du Vieux Bureau</v>
+        <v>30 Rue de l'Espierre</v>
       </c>
       <c r="X36" t="str">
-        <v>59150</v>
+        <v>59100</v>
       </c>
       <c r="Y36" t="str">
-        <v>Wattrelos</v>
+        <v>Roubaix</v>
       </c>
       <c r="Z36" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA36" t="str">
+        <v>QN05980M</v>
       </c>
       <c r="AB36" t="str">
         <v>Non</v>
@@ -5823,66 +5994,72 @@
         <v>Non</v>
       </c>
       <c r="AK36" t="str">
-        <v>236h30m</v>
+        <v>355h</v>
       </c>
       <c r="AL36" t="str">
-        <v>155h</v>
+        <v>294h</v>
       </c>
       <c r="AM36" t="str">
-        <v>120h45m</v>
+        <v>108h</v>
       </c>
       <c r="AN36" s="1">
-        <v>46035.58021990741</v>
+        <v>46031.58672453704</v>
+      </c>
+      <c r="AO36" s="1">
+        <v>46080.50069444445</v>
+      </c>
+      <c r="AP36" s="1">
+        <v>46307.40138888889</v>
       </c>
       <c r="AU36" s="1">
-        <v>46000.606944444444</v>
+        <v>46000</v>
       </c>
       <c r="AV36" t="str">
-        <v>MISSION LOCALE WATTRELOS - LEERS</v>
+        <v>En direct</v>
       </c>
       <c r="AX36" s="1">
-        <v>45999.60902777778</v>
+        <v>46000</v>
       </c>
       <c r="BA36" t="str">
         <v>NON</v>
       </c>
       <c r="BG36" t="str">
-        <v>9460</v>
+        <v>9434</v>
       </c>
       <c r="BJ36" t="str">
-        <v>24438f74-6789-4524-b70a-4879fa29d9a1</v>
+        <v>6835accf-9cb9-4060-b9fa-41d8eb993467</v>
       </c>
       <c r="BK36" t="str">
         <v>Accepted</v>
       </c>
       <c r="BL36" t="str">
-        <v>18/03/26 : J'ai des idées &gt; je sais : Audiovisuelle/Évenementie</v>
+        <v/>
       </c>
       <c r="BM36" t="str">
         <v/>
       </c>
       <c r="BN36" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/l_djemoui_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fl%5Fdjemoui%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FE2C&amp;ga=1</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>76124</v>
+        <v>56006</v>
       </c>
       <c r="B37" t="str">
         <v>Femme</v>
       </c>
       <c r="C37" t="str">
-        <v>BOUTRAA</v>
+        <v>DELECOURT</v>
       </c>
       <c r="D37" t="str">
-        <v>Lilia</v>
+        <v>Alicia</v>
       </c>
       <c r="E37" t="str">
-        <v>l.boutraa@e2c-grandlille.fr</v>
+        <v>a.delecourt@e2c-grandlille.fr</v>
       </c>
       <c r="F37" t="str">
-        <v>0604436838</v>
+        <v>0646122087</v>
       </c>
       <c r="G37" t="str">
         <v>Grand Lille</v>
@@ -5891,31 +6068,31 @@
         <v>Roubaix</v>
       </c>
       <c r="I37" t="str">
-        <v>Auxiliaire de vie</v>
+        <v>Accompagnateur médicosocial / Accompagnatrice médicosociale de personnes dépendantes, Aide-soignant / Aide-soignante en puériculture</v>
       </c>
       <c r="K37" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L37" t="str">
-        <v>référés Sarah</v>
+        <v>référés Rosetta</v>
       </c>
       <c r="M37" t="str">
         <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O37" t="str">
-        <v>MORVAN Sarah</v>
+        <v>COLACCINO Rosetta</v>
       </c>
       <c r="P37">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q37">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R37" s="1">
-        <v>36866</v>
+        <v>37689</v>
       </c>
       <c r="T37" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v>ROUBAIX, FRANCE</v>
       </c>
       <c r="U37" t="str">
         <v>FRANCAISE</v>
@@ -5924,19 +6101,16 @@
         <v>OUI</v>
       </c>
       <c r="W37" t="str">
-        <v>129 Avenue du Président Kennedy</v>
+        <v>23 23 Rue d'Arcole</v>
       </c>
       <c r="X37" t="str">
-        <v>59100</v>
+        <v>59170</v>
       </c>
       <c r="Y37" t="str">
-        <v>Roubaix</v>
+        <v>CROIX</v>
       </c>
       <c r="Z37" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA37" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB37" t="str">
         <v>Non</v>
@@ -5945,7 +6119,7 @@
         <v>NON</v>
       </c>
       <c r="AD37" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE37" t="str">
         <v>Non</v>
@@ -5966,34 +6140,40 @@
         <v>Non</v>
       </c>
       <c r="AK37" t="str">
-        <v>254h</v>
+        <v>287h45m</v>
       </c>
       <c r="AL37" t="str">
-        <v>235h45m</v>
+        <v>309h10m</v>
       </c>
       <c r="AM37" t="str">
-        <v>90h30m</v>
+        <v>156h45m</v>
       </c>
       <c r="AN37" s="1">
-        <v>46035.57386574074</v>
+        <v>46035.57910879629</v>
+      </c>
+      <c r="AO37" s="1">
+        <v>46080.49444444444</v>
+      </c>
+      <c r="AP37" s="1">
+        <v>46307.49513888889</v>
       </c>
       <c r="AU37" s="1">
-        <v>45974.48888888889</v>
+        <v>46000</v>
       </c>
       <c r="AV37" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
+        <v>MISSION LOCALE VAL DE MARQUE - Croix</v>
       </c>
       <c r="AX37" s="1">
-        <v>45971.51180555556</v>
+        <v>46000</v>
       </c>
       <c r="BA37" t="str">
         <v>NON</v>
       </c>
       <c r="BG37" t="str">
-        <v>9429</v>
+        <v>9432</v>
       </c>
       <c r="BJ37" t="str">
-        <v>fd0b5750-cd85-4f25-bbd6-e77394dde325</v>
+        <v>355c59e2-6b1f-4187-bfb9-19f668e80597</v>
       </c>
       <c r="BK37" t="str">
         <v>Accepted</v>
@@ -6010,22 +6190,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>76109</v>
+        <v>55900</v>
       </c>
       <c r="B38" t="str">
         <v>Femme</v>
       </c>
       <c r="C38" t="str">
-        <v>SINNAEVE</v>
+        <v>DAHMANI</v>
       </c>
       <c r="D38" t="str">
-        <v>Ambre</v>
+        <v>Sania</v>
       </c>
       <c r="E38" t="str">
-        <v>a.sinnaeve@e2c-grandlille.fr</v>
+        <v>s.dahmani@e2c-grandlille.fr</v>
       </c>
       <c r="F38" t="str">
-        <v>0786814938</v>
+        <v>0786502194</v>
       </c>
       <c r="G38" t="str">
         <v>Grand Lille</v>
@@ -6034,34 +6214,34 @@
         <v>Roubaix</v>
       </c>
       <c r="I38" t="str">
-        <v>Moniteur éducateur / Monitrice éducatrice</v>
+        <v>Accompagnant éducatif et social / Accompagnante éducative et sociale en milieu scolaire</v>
       </c>
       <c r="K38" t="str">
         <v>Je sais</v>
       </c>
       <c r="L38" t="str">
-        <v>référés David</v>
+        <v>référés Rosetta</v>
       </c>
       <c r="M38" t="str">
         <v>2601/janvier 2026 RBX</v>
       </c>
       <c r="O38" t="str">
-        <v>KIMPE David</v>
+        <v>COLACCINO Rosetta</v>
       </c>
       <c r="P38">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q38">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R38" s="1">
-        <v>38839</v>
+        <v>40042</v>
       </c>
       <c r="S38" t="str">
-        <v>SINNAEVE</v>
+        <v>Dahmani</v>
       </c>
       <c r="T38" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v>VILLENEUVE D'ASCQ, FRANCE</v>
       </c>
       <c r="U38" t="str">
         <v>FRANCAISE</v>
@@ -6070,13 +6250,13 @@
         <v>OUI</v>
       </c>
       <c r="W38" t="str">
-        <v>23 Rue la Fontaine</v>
+        <v>5 5 Square du Laboureur</v>
       </c>
       <c r="X38" t="str">
-        <v>59250</v>
+        <v>59150</v>
       </c>
       <c r="Y38" t="str">
-        <v>Halluin</v>
+        <v>WATTRELOS</v>
       </c>
       <c r="Z38" t="str">
         <v>Non</v>
@@ -6088,7 +6268,7 @@
         <v>NON</v>
       </c>
       <c r="AD38" t="str">
-        <v>3 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE38" t="str">
         <v>Non</v>
@@ -6109,37 +6289,55 @@
         <v>Non</v>
       </c>
       <c r="AK38" t="str">
-        <v>207h</v>
+        <v>321h30m</v>
       </c>
       <c r="AL38" t="str">
-        <v>206h</v>
+        <v>308h30m</v>
       </c>
       <c r="AM38" t="str">
-        <v>124h</v>
+        <v>142h</v>
       </c>
       <c r="AN38" s="1">
-        <v>46035.60104166667</v>
+        <v>46035.57434027778</v>
+      </c>
+      <c r="AO38" s="1">
+        <v>46104.464583333334</v>
+      </c>
+      <c r="AP38" s="1">
+        <v>46307.43125</v>
       </c>
       <c r="AU38" s="1">
-        <v>45974.48055555556</v>
+        <v>45965</v>
       </c>
       <c r="AV38" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
-      </c>
-      <c r="AW38" t="str">
-        <v>M. GRACA Marques</v>
+        <v>POLE EMPLOI -Wattrelos</v>
       </c>
       <c r="AX38" s="1">
-        <v>45971.48611111111</v>
+        <v>45958</v>
       </c>
       <c r="BA38" t="str">
         <v>NON</v>
       </c>
+      <c r="BB38" t="str">
+        <v xml:space="preserve">BENYOUB </v>
+      </c>
+      <c r="BC38" t="str">
+        <v xml:space="preserve">Kheira </v>
+      </c>
+      <c r="BD38" t="str">
+        <v>5 Square du Laboureur, 59150 WATTRELOS</v>
+      </c>
+      <c r="BE38" t="str">
+        <v>0620899204</v>
+      </c>
+      <c r="BF38" t="str">
+        <v>benyoub.kheira@hotmail.fr</v>
+      </c>
       <c r="BG38" t="str">
-        <v>9419</v>
+        <v>9422</v>
       </c>
       <c r="BJ38" t="str">
-        <v>286b045d-d9f4-429a-8036-4fa8cf6d9c28</v>
+        <v>fd740b9b-5a78-4bdd-9905-574c15ad8906</v>
       </c>
       <c r="BK38" t="str">
         <v>Accepted</v>
@@ -6156,22 +6354,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>75853</v>
+        <v>36754</v>
       </c>
       <c r="B39" t="str">
         <v>Homme</v>
       </c>
       <c r="C39" t="str">
-        <v>GHERBI</v>
+        <v>LEMAIRE</v>
       </c>
       <c r="D39" t="str">
-        <v>Mohamed</v>
+        <v>Lello</v>
       </c>
       <c r="E39" t="str">
-        <v>m.gherbi@e2c-grandlille.fr</v>
+        <v>lello9454@gmail.com</v>
       </c>
       <c r="F39" t="str">
-        <v>0632937661</v>
+        <v>0749743176</v>
       </c>
       <c r="G39" t="str">
         <v>Grand Lille</v>
@@ -6180,52 +6378,52 @@
         <v>Roubaix</v>
       </c>
       <c r="I39" t="str">
-        <v>Développeur / Développeuse full-stack, Analyste en cybersécurité</v>
+        <v>Infirmier / Infirmière en soins généraux (IDE)</v>
       </c>
       <c r="K39" t="str">
-        <v>J'ai des idées</v>
+        <v>J'y vais</v>
       </c>
       <c r="L39" t="str">
-        <v>référés Sabah</v>
+        <v>référés Sarah</v>
       </c>
       <c r="M39" t="str">
-        <v>2601/janvier 2026 RBX</v>
+        <v>2511/novembre 2025 RBX</v>
       </c>
       <c r="O39" t="str">
-        <v>SELAM Sabah</v>
+        <v>MORVAN Sarah</v>
       </c>
       <c r="P39">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q39">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R39" s="1">
-        <v>38380</v>
+        <v>39499</v>
+      </c>
+      <c r="S39" t="str">
+        <v>Lemaire</v>
       </c>
       <c r="T39" t="str">
-        <v xml:space="preserve">Roubaix </v>
+        <v>CROIX</v>
       </c>
       <c r="U39" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V39" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="W39" t="str">
-        <v>26 Rue de Cassel</v>
+        <v>76 76 Rue des Camélias</v>
       </c>
       <c r="X39" t="str">
-        <v>59100</v>
+        <v>59390</v>
       </c>
       <c r="Y39" t="str">
-        <v>Roubaix</v>
+        <v>LYS-LEZ-LANNOY</v>
       </c>
       <c r="Z39" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA39" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB39" t="str">
         <v>Non</v>
@@ -6234,10 +6432,10 @@
         <v>NON</v>
       </c>
       <c r="AD39" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE39" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF39" t="str">
         <v>Non</v>
@@ -6255,37 +6453,34 @@
         <v>Non</v>
       </c>
       <c r="AK39" t="str">
-        <v>329h30m</v>
+        <v>405h45m</v>
       </c>
       <c r="AL39" t="str">
-        <v>273h</v>
+        <v>316h30m</v>
       </c>
       <c r="AM39" t="str">
-        <v>32h30m</v>
+        <v>196h30m</v>
       </c>
       <c r="AN39" s="1">
-        <v>46035.58324074074</v>
-      </c>
-      <c r="AU39" s="1">
-        <v>46000.6</v>
+        <v>45964</v>
+      </c>
+      <c r="AO39" s="1">
+        <v>46038</v>
+      </c>
+      <c r="AP39" s="1">
+        <v>46237.083333333336</v>
       </c>
       <c r="AV39" t="str">
-        <v>POLE EMPLOI -Roubaix-</v>
-      </c>
-      <c r="AW39" t="str">
-        <v>France Travail</v>
-      </c>
-      <c r="AX39" s="1">
-        <v>45999.663194444445</v>
+        <v>MISSION LOCALE MNO - Antenne Lambersart</v>
       </c>
       <c r="BA39" t="str">
         <v>NON</v>
       </c>
       <c r="BG39" t="str">
-        <v>9440</v>
+        <v>597090</v>
       </c>
       <c r="BJ39" t="str">
-        <v>06147ccf-6046-47b1-b554-e87a89854202</v>
+        <v>922807a6-e7fe-4be1-a652-5cfb8c1ceb8c</v>
       </c>
       <c r="BK39" t="str">
         <v>Accepted</v>
@@ -6302,22 +6497,19 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>57580</v>
+        <v>36745</v>
       </c>
       <c r="B40" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C40" t="str">
-        <v>ROUIBI</v>
+        <v>MAC-DONALD</v>
       </c>
       <c r="D40" t="str">
-        <v>Ambre Soulef</v>
+        <v>Renato</v>
       </c>
       <c r="E40" t="str">
-        <v>as.rouibi@e2c-grandlille.fr</v>
-      </c>
-      <c r="F40" t="str">
-        <v>0777887359</v>
+        <v>macdonaldrenato4@gmail.com</v>
       </c>
       <c r="G40" t="str">
         <v>Grand Lille</v>
@@ -6325,6 +6517,9 @@
       <c r="H40" t="str">
         <v>Roubaix</v>
       </c>
+      <c r="I40" t="str">
+        <v>Vendeur / Vendeuse en accessoires de la personne</v>
+      </c>
       <c r="K40" t="str">
         <v>Je sais</v>
       </c>
@@ -6332,34 +6527,34 @@
         <v>référés Sabah</v>
       </c>
       <c r="M40" t="str">
-        <v>2601/janvier 2026 RBX</v>
+        <v>2511/novembre 2025 RBX</v>
       </c>
       <c r="O40" t="str">
         <v>SELAM Sabah</v>
       </c>
       <c r="P40">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q40">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R40" s="1">
-        <v>38091</v>
+        <v>38855</v>
       </c>
       <c r="S40" t="str">
-        <v>ROUIBI</v>
+        <v>MAC-DONALD</v>
       </c>
       <c r="T40" t="str">
-        <v>ROUBAIX, FRANCE</v>
+        <v>SAINT-LAURENT DU MARONI, GUYANE FRANÇAISE</v>
       </c>
       <c r="U40" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V40" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="W40" t="str">
-        <v>32 32 Rue Reaumur</v>
+        <v>12 12 Rue Paul Claudel</v>
       </c>
       <c r="X40" t="str">
         <v>59100</v>
@@ -6380,7 +6575,7 @@
         <v>NON</v>
       </c>
       <c r="AD40" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE40" t="str">
         <v>Non</v>
@@ -6401,37 +6596,34 @@
         <v>Non</v>
       </c>
       <c r="AK40" t="str">
-        <v>291h15m</v>
+        <v>489h</v>
       </c>
       <c r="AL40" t="str">
-        <v>163h30m</v>
+        <v>399h</v>
       </c>
       <c r="AM40" t="str">
-        <v>43h45m</v>
+        <v>161h30m</v>
       </c>
       <c r="AN40" s="1">
-        <v>46035.600752314815</v>
-      </c>
-      <c r="AU40" s="1">
-        <v>46000</v>
+        <v>45964</v>
+      </c>
+      <c r="AO40" s="1">
+        <v>46028.67222222222</v>
+      </c>
+      <c r="AP40" s="1">
+        <v>46237.083333333336</v>
       </c>
       <c r="AV40" t="str">
-        <v>POLE EMPLOI -Roubaix-</v>
-      </c>
-      <c r="AW40" t="str">
-        <v>France Travail Mme MAHIEU</v>
-      </c>
-      <c r="AX40" s="1">
-        <v>46000</v>
+        <v>En direct</v>
       </c>
       <c r="BA40" t="str">
         <v>NON</v>
       </c>
       <c r="BG40" t="str">
-        <v>9459</v>
+        <v>597092</v>
       </c>
       <c r="BJ40" t="str">
-        <v>e09f752b-5046-430d-b43f-2b35d07e8180</v>
+        <v>c522c80a-5a53-4584-a358-08d638df994e</v>
       </c>
       <c r="BK40" t="str">
         <v>Accepted</v>
@@ -6443,2160 +6635,12 @@
         <v/>
       </c>
       <c r="BN40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>57343</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C41" t="str">
-        <v>NOPPE</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Sébastien</v>
-      </c>
-      <c r="E41" t="str">
-        <v>s.noppe@e2c-grandlille.fr</v>
-      </c>
-      <c r="F41" t="str">
-        <v>0667697331</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H41" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I41" t="str">
-        <v>Accompagnateur / Accompagnatrice de voyages ou d'activités culturelles, sportives et de plein air</v>
-      </c>
-      <c r="K41" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L41" t="str">
-        <v>référés Rosetta</v>
-      </c>
-      <c r="M41" t="str">
-        <v>2601/janvier 2026 RBX</v>
-      </c>
-      <c r="O41" t="str">
-        <v>COLACCINO Rosetta</v>
-      </c>
-      <c r="P41">
-        <v>19</v>
-      </c>
-      <c r="Q41">
-        <v>18</v>
-      </c>
-      <c r="R41" s="1">
-        <v>39116</v>
-      </c>
-      <c r="T41" t="str">
-        <v>ROUBAIX, FRANCE</v>
-      </c>
-      <c r="W41" t="str">
-        <v>14 14 Chemin des Chasses</v>
-      </c>
-      <c r="X41" t="str">
-        <v>59115</v>
-      </c>
-      <c r="Y41" t="str">
-        <v>LEERS</v>
-      </c>
-      <c r="Z41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC41" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD41" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG41" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ41" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK41" t="str">
-        <v>225h30m</v>
-      </c>
-      <c r="AL41" t="str">
-        <v>242h</v>
-      </c>
-      <c r="AM41" t="str">
-        <v>118h30m</v>
-      </c>
-      <c r="AN41" s="1">
-        <v>46035.60050925926</v>
-      </c>
-      <c r="AU41" s="1">
-        <v>45979</v>
-      </c>
-      <c r="AV41" t="str">
-        <v>MISSION LOCALE WATTRELOS - LEERS</v>
-      </c>
-      <c r="AW41" t="str">
-        <v>Sébastien MULDERMANS</v>
-      </c>
-      <c r="AX41" s="1">
-        <v>45979</v>
-      </c>
-      <c r="BA41" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG41" t="str">
-        <v>9457</v>
-      </c>
-      <c r="BJ41" t="str">
-        <v>166a1377-45a2-4f92-bb7a-efc5599d19fb</v>
-      </c>
-      <c r="BK41" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL41" t="str">
-        <v/>
-      </c>
-      <c r="BM41" t="str">
-        <v/>
-      </c>
-      <c r="BN41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>57232</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C42" t="str">
-        <v>MEZIANI</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Ilian</v>
-      </c>
-      <c r="E42" t="str">
-        <v>i.meziani@e2c-grandlille.fr</v>
-      </c>
-      <c r="F42" t="str">
-        <v>0614790289</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H42" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I42" t="str">
-        <v>Animateur / Animatrice d'activités audiovisuelles, Assistant monteur / Assistante monteuse audiovisuel, Vendeur / Vendeuse en boulangerie-pâtisserie</v>
-      </c>
-      <c r="K42" t="str">
-        <v>J'explore</v>
-      </c>
-      <c r="L42" t="str">
-        <v>référés Alexia</v>
-      </c>
-      <c r="M42" t="str">
-        <v>2601/janvier 2026 RBX</v>
-      </c>
-      <c r="O42" t="str">
-        <v>ARNAUD Alexia</v>
-      </c>
-      <c r="P42">
-        <v>19</v>
-      </c>
-      <c r="Q42">
-        <v>18</v>
-      </c>
-      <c r="R42" s="1">
-        <v>39163</v>
-      </c>
-      <c r="T42" t="str">
-        <v>TOURCOING, FRANCE</v>
-      </c>
-      <c r="W42" t="str">
-        <v>12 12 Rue Fromé</v>
-      </c>
-      <c r="X42" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y42" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z42" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA42" t="str">
-        <v>QN05980M</v>
-      </c>
-      <c r="AB42" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC42" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD42" t="str">
-        <v>4 validé</v>
-      </c>
-      <c r="AE42" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF42" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG42" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH42" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI42" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ42" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK42" t="str">
-        <v>236h45m</v>
-      </c>
-      <c r="AL42" t="str">
-        <v>238h</v>
-      </c>
-      <c r="AM42" t="str">
-        <v>117h15m</v>
-      </c>
-      <c r="AN42" s="1">
-        <v>46035.599710648145</v>
-      </c>
-      <c r="AU42" s="1">
-        <v>45988</v>
-      </c>
-      <c r="AV42" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
-      </c>
-      <c r="AX42" s="1">
-        <v>45986</v>
-      </c>
-      <c r="BA42" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG42" t="str">
-        <v>9452</v>
-      </c>
-      <c r="BJ42" t="str">
-        <v>8ea45b31-b6de-4d0d-86de-c2886c002a2a</v>
-      </c>
-      <c r="BK42" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL42" t="str">
-        <v/>
-      </c>
-      <c r="BM42" t="str">
-        <v/>
-      </c>
-      <c r="BN42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>56266</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C43" t="str">
-        <v>DOUDJEDID</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Amayes</v>
-      </c>
-      <c r="E43" t="str">
-        <v>a.doudjedid@e2c-grandlille.fr</v>
-      </c>
-      <c r="F43" t="str">
-        <v>0745840498</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H43" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I43" t="str">
-        <v>Aide-soignant / Aide-soignante, Éducateur / Éducatrice de jeunes enfants</v>
-      </c>
-      <c r="K43" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L43" t="str">
-        <v>référés Sabah</v>
-      </c>
-      <c r="M43" t="str">
-        <v>2601/janvier 2026 RBX</v>
-      </c>
-      <c r="O43" t="str">
-        <v>SELAM Sabah</v>
-      </c>
-      <c r="P43">
-        <v>21</v>
-      </c>
-      <c r="Q43">
-        <v>20</v>
-      </c>
-      <c r="R43" s="1">
-        <v>38463</v>
-      </c>
-      <c r="T43" t="str">
-        <v>ROUBAIX, FRANCE</v>
-      </c>
-      <c r="U43" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V43" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W43" t="str">
-        <v>31 31 Rue de l'Espierre</v>
-      </c>
-      <c r="X43" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y43" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC43" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD43" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG43" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ43" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK43" t="str">
-        <v>311h30m</v>
-      </c>
-      <c r="AL43" t="str">
-        <v>238h</v>
-      </c>
-      <c r="AM43" t="str">
-        <v>37h15m</v>
-      </c>
-      <c r="AN43" s="1">
-        <v>46031.58672453704</v>
-      </c>
-      <c r="AP43" s="1">
-        <v>46307.40138888889</v>
-      </c>
-      <c r="AU43" s="1">
-        <v>46000</v>
-      </c>
-      <c r="AV43" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="AX43" s="1">
-        <v>46000</v>
-      </c>
-      <c r="BA43" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG43" t="str">
-        <v>9434</v>
-      </c>
-      <c r="BJ43" t="str">
-        <v>6835accf-9cb9-4060-b9fa-41d8eb993467</v>
-      </c>
-      <c r="BK43" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL43" t="str">
-        <v/>
-      </c>
-      <c r="BM43" t="str">
-        <v/>
-      </c>
-      <c r="BN43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>56006</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C44" t="str">
-        <v>DELECOURT</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Alicia</v>
-      </c>
-      <c r="E44" t="str">
-        <v>a.delecourt@e2c-grandlille.fr</v>
-      </c>
-      <c r="F44" t="str">
-        <v>0646122087</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H44" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I44" t="str">
-        <v>Accompagnateur médicosocial / Accompagnatrice médicosociale de personnes dépendantes, Aide-soignant / Aide-soignante en puériculture</v>
-      </c>
-      <c r="K44" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L44" t="str">
-        <v>référés Rosetta</v>
-      </c>
-      <c r="M44" t="str">
-        <v>2601/janvier 2026 RBX</v>
-      </c>
-      <c r="O44" t="str">
-        <v>COLACCINO Rosetta</v>
-      </c>
-      <c r="P44">
-        <v>23</v>
-      </c>
-      <c r="Q44">
-        <v>22</v>
-      </c>
-      <c r="R44" s="1">
-        <v>37689</v>
-      </c>
-      <c r="T44" t="str">
-        <v>ROUBAIX, FRANCE</v>
-      </c>
-      <c r="U44" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V44" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="W44" t="str">
-        <v>23 23 Rue d'Arcole</v>
-      </c>
-      <c r="X44" t="str">
-        <v>59170</v>
-      </c>
-      <c r="Y44" t="str">
-        <v>CROIX</v>
-      </c>
-      <c r="Z44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC44" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD44" t="str">
-        <v>4 validé</v>
-      </c>
-      <c r="AE44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG44" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ44" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK44" t="str">
-        <v>227h</v>
-      </c>
-      <c r="AL44" t="str">
-        <v>309h10m</v>
-      </c>
-      <c r="AM44" t="str">
-        <v>73h30m</v>
-      </c>
-      <c r="AN44" s="1">
-        <v>46035.57910879629</v>
-      </c>
-      <c r="AU44" s="1">
-        <v>46000</v>
-      </c>
-      <c r="AV44" t="str">
-        <v>MISSION LOCALE VAL DE MARQUE - Croix</v>
-      </c>
-      <c r="AX44" s="1">
-        <v>46000</v>
-      </c>
-      <c r="BA44" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG44" t="str">
-        <v>9432</v>
-      </c>
-      <c r="BJ44" t="str">
-        <v>355c59e2-6b1f-4187-bfb9-19f668e80597</v>
-      </c>
-      <c r="BK44" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL44" t="str">
-        <v/>
-      </c>
-      <c r="BM44" t="str">
-        <v/>
-      </c>
-      <c r="BN44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>55900</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C45" t="str">
-        <v>DAHMANI</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Sania</v>
-      </c>
-      <c r="E45" t="str">
-        <v>s.dahmani@e2c-grandlille.fr</v>
-      </c>
-      <c r="F45" t="str">
-        <v>0786502194</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H45" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I45" t="str">
-        <v>Accompagnant éducatif et social / Accompagnante éducative et sociale en milieu scolaire</v>
-      </c>
-      <c r="K45" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L45" t="str">
-        <v>référés Rosetta</v>
-      </c>
-      <c r="M45" t="str">
-        <v>2601/janvier 2026 RBX</v>
-      </c>
-      <c r="O45" t="str">
-        <v>COLACCINO Rosetta</v>
-      </c>
-      <c r="P45">
-        <v>16</v>
-      </c>
-      <c r="Q45">
-        <v>16</v>
-      </c>
-      <c r="R45" s="1">
-        <v>40042</v>
-      </c>
-      <c r="S45" t="str">
-        <v>Dahmani</v>
-      </c>
-      <c r="T45" t="str">
-        <v>VILLENEUVE D'ASCQ, FRANCE</v>
-      </c>
-      <c r="U45" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V45" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="W45" t="str">
-        <v>5 5 Square du Laboureur</v>
-      </c>
-      <c r="X45" t="str">
-        <v>59150</v>
-      </c>
-      <c r="Y45" t="str">
-        <v>WATTRELOS</v>
-      </c>
-      <c r="Z45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC45" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD45" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG45" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ45" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK45" t="str">
-        <v>251h</v>
-      </c>
-      <c r="AL45" t="str">
-        <v>246h30m</v>
-      </c>
-      <c r="AM45" t="str">
-        <v>106h45m</v>
-      </c>
-      <c r="AN45" s="1">
-        <v>46035.57434027778</v>
-      </c>
-      <c r="AP45" s="1">
-        <v>46307.43125</v>
-      </c>
-      <c r="AU45" s="1">
-        <v>45965</v>
-      </c>
-      <c r="AV45" t="str">
-        <v>POLE EMPLOI -Wattrelos</v>
-      </c>
-      <c r="AX45" s="1">
-        <v>45958</v>
-      </c>
-      <c r="BA45" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BB45" t="str">
-        <v xml:space="preserve">BENYOUB </v>
-      </c>
-      <c r="BC45" t="str">
-        <v xml:space="preserve">Kheira </v>
-      </c>
-      <c r="BD45" t="str">
-        <v>5 Square du Laboureur, 59150 WATTRELOS</v>
-      </c>
-      <c r="BE45" t="str">
-        <v>0620899204</v>
-      </c>
-      <c r="BF45" t="str">
-        <v>benyoub.kheira@hotmail.fr</v>
-      </c>
-      <c r="BG45" t="str">
-        <v>9422</v>
-      </c>
-      <c r="BJ45" t="str">
-        <v>fd740b9b-5a78-4bdd-9905-574c15ad8906</v>
-      </c>
-      <c r="BK45" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL45" t="str">
-        <v/>
-      </c>
-      <c r="BM45" t="str">
-        <v/>
-      </c>
-      <c r="BN45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>55175</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C46" t="str">
-        <v>POLLET</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Donovan</v>
-      </c>
-      <c r="E46" t="str">
-        <v>d.pollet@e2c-grandlille.fr</v>
-      </c>
-      <c r="F46" t="str">
-        <v>0625438633</v>
-      </c>
-      <c r="G46" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H46" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I46" t="str">
-        <v>Employé polyvalent / Employée polyvalente de restauration</v>
-      </c>
-      <c r="K46" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L46" t="str">
-        <v>référés David</v>
-      </c>
-      <c r="M46" t="str">
-        <v>2511/novembre 2025 RBX</v>
-      </c>
-      <c r="O46" t="str">
-        <v>KIMPE David</v>
-      </c>
-      <c r="P46">
-        <v>21</v>
-      </c>
-      <c r="Q46">
-        <v>20</v>
-      </c>
-      <c r="R46" s="1">
-        <v>38451</v>
-      </c>
-      <c r="S46" t="str">
-        <v>POLLET</v>
-      </c>
-      <c r="T46" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="U46" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W46" t="str">
-        <v>172 172 Avenue Jules Brame</v>
-      </c>
-      <c r="X46" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y46" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z46" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA46" t="str">
-        <v>QN05980M</v>
-      </c>
-      <c r="AB46" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC46" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD46" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE46" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF46" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG46" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH46" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI46" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ46" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK46" t="str">
-        <v>253h15m</v>
-      </c>
-      <c r="AL46" t="str">
-        <v>261h30m</v>
-      </c>
-      <c r="AM46" t="str">
-        <v>159h45m</v>
-      </c>
-      <c r="AN46" s="1">
-        <v>45964</v>
-      </c>
-      <c r="AP46" s="1">
-        <v>46237.083333333336</v>
-      </c>
-      <c r="AV46" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA46" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG46" t="str">
-        <v>597166</v>
-      </c>
-      <c r="BJ46" t="str">
-        <v>89caeaec-a976-41a7-be7b-ebe350c939ee</v>
-      </c>
-      <c r="BK46" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL46" t="str">
-        <v/>
-      </c>
-      <c r="BM46" t="str">
-        <v/>
-      </c>
-      <c r="BN46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>39137</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C47" t="str">
-        <v>DERAEDT</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Neyla</v>
-      </c>
-      <c r="E47" t="str">
-        <v>neyla.deraedt592424@gmail.com</v>
-      </c>
-      <c r="F47" t="str">
-        <v>0601868325</v>
-      </c>
-      <c r="G47" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H47" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I47" t="str">
-        <v>Auxiliaire de puériculture, Animateur / Animatrice petite enfance</v>
-      </c>
-      <c r="K47" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L47" t="str">
-        <v>référés Alexia</v>
-      </c>
-      <c r="M47" t="str">
-        <v>2509/septembre 2 2025 RBX</v>
-      </c>
-      <c r="O47" t="str">
-        <v>ARNAUD Alexia</v>
-      </c>
-      <c r="P47">
-        <v>17</v>
-      </c>
-      <c r="Q47">
-        <v>16</v>
-      </c>
-      <c r="R47" s="1">
-        <v>39745</v>
-      </c>
-      <c r="S47" t="str">
-        <v>Deraedt</v>
-      </c>
-      <c r="T47" t="str">
-        <v>VILLENEUVE D'ASCQ</v>
-      </c>
-      <c r="U47" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V47" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W47" t="str">
-        <v>68 68 Rue Louis Armand</v>
-      </c>
-      <c r="X47" t="str">
-        <v>59150</v>
-      </c>
-      <c r="Y47" t="str">
-        <v>WATTRELOS</v>
-      </c>
-      <c r="Z47" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB47" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC47" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD47" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE47" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AF47" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG47" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH47" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI47" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ47" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK47" t="str">
-        <v>404h45m</v>
-      </c>
-      <c r="AL47" t="str">
-        <v>349h20m</v>
-      </c>
-      <c r="AM47" t="str">
-        <v>83h45m</v>
-      </c>
-      <c r="AN47" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO47" s="1">
-        <v>45982.041666666664</v>
-      </c>
-      <c r="AP47" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV47" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA47" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG47" t="str">
-        <v>595582</v>
-      </c>
-      <c r="BJ47" t="str">
-        <v>3647a2e3-2b62-4957-9c05-4adcd4b5542d</v>
-      </c>
-      <c r="BK47" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL47" t="str">
-        <v/>
-      </c>
-      <c r="BM47" t="str">
-        <v/>
-      </c>
-      <c r="BN47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>36754</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C48" t="str">
-        <v>LEMAIRE</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Lello</v>
-      </c>
-      <c r="E48" t="str">
-        <v>lello9454@gmail.com</v>
-      </c>
-      <c r="F48" t="str">
-        <v>0749743176</v>
-      </c>
-      <c r="G48" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H48" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I48" t="str">
-        <v>Infirmier / Infirmière en soins généraux (IDE)</v>
-      </c>
-      <c r="K48" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L48" t="str">
-        <v>référés Sarah</v>
-      </c>
-      <c r="M48" t="str">
-        <v>2511/novembre 2025 RBX</v>
-      </c>
-      <c r="O48" t="str">
-        <v>MORVAN Sarah</v>
-      </c>
-      <c r="P48">
-        <v>18</v>
-      </c>
-      <c r="Q48">
-        <v>17</v>
-      </c>
-      <c r="R48" s="1">
-        <v>39499</v>
-      </c>
-      <c r="S48" t="str">
-        <v>Lemaire</v>
-      </c>
-      <c r="T48" t="str">
-        <v>CROIX</v>
-      </c>
-      <c r="U48" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V48" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W48" t="str">
-        <v>76 76 Rue des Camélias</v>
-      </c>
-      <c r="X48" t="str">
-        <v>59390</v>
-      </c>
-      <c r="Y48" t="str">
-        <v>LYS-LEZ-LANNOY</v>
-      </c>
-      <c r="Z48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC48" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD48" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG48" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ48" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK48" t="str">
-        <v>326h45m</v>
-      </c>
-      <c r="AL48" t="str">
-        <v>264h30m</v>
-      </c>
-      <c r="AM48" t="str">
-        <v>153h</v>
-      </c>
-      <c r="AN48" s="1">
-        <v>45964</v>
-      </c>
-      <c r="AP48" s="1">
-        <v>46237.083333333336</v>
-      </c>
-      <c r="AV48" t="str">
-        <v>MISSION LOCALE MNO - Antenne Lambersart</v>
-      </c>
-      <c r="BA48" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG48" t="str">
-        <v>597090</v>
-      </c>
-      <c r="BJ48" t="str">
-        <v>922807a6-e7fe-4be1-a652-5cfb8c1ceb8c</v>
-      </c>
-      <c r="BK48" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL48" t="str">
-        <v/>
-      </c>
-      <c r="BM48" t="str">
-        <v/>
-      </c>
-      <c r="BN48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>36747</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C49" t="str">
-        <v>CHARABI</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Hussen</v>
-      </c>
-      <c r="E49" t="str">
-        <v>charabihussen@gmail.com</v>
-      </c>
-      <c r="F49" t="str">
-        <v>0763623290</v>
-      </c>
-      <c r="G49" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H49" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I49" t="str">
-        <v>Préparateur / Préparatrice au drive</v>
-      </c>
-      <c r="L49" t="str">
-        <v>référés Loic</v>
-      </c>
-      <c r="M49" t="str">
-        <v>2511/novembre 2025 RBX</v>
-      </c>
-      <c r="O49" t="str">
-        <v>DUCARME Loïc</v>
-      </c>
-      <c r="P49">
-        <v>20</v>
-      </c>
-      <c r="Q49">
-        <v>19</v>
-      </c>
-      <c r="R49" s="1">
-        <v>38740</v>
-      </c>
-      <c r="S49" t="str">
-        <v>CHARABI</v>
-      </c>
-      <c r="T49" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="U49" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V49" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W49" t="str">
-        <v>73 73 Rue de Crouy</v>
-      </c>
-      <c r="X49" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y49" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z49" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA49" t="str">
-        <v>QN05980M</v>
-      </c>
-      <c r="AB49" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC49" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD49" t="str">
-        <v>3 non validé</v>
-      </c>
-      <c r="AE49" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF49" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG49" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH49" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI49" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ49" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK49" t="str">
-        <v>328h30m</v>
-      </c>
-      <c r="AL49" t="str">
-        <v>140h</v>
-      </c>
-      <c r="AM49" t="str">
-        <v>196h15m</v>
-      </c>
-      <c r="AN49" s="1">
-        <v>45964</v>
-      </c>
-      <c r="AO49" s="1">
-        <v>46147.55980324074</v>
-      </c>
-      <c r="AP49" s="1">
-        <v>46237.083333333336</v>
-      </c>
-      <c r="AV49" t="str">
-        <v>FORUM</v>
-      </c>
-      <c r="BA49" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG49" t="str">
-        <v>597087</v>
-      </c>
-      <c r="BJ49" t="str">
-        <v>1728d8e5-984d-45a2-8fa4-f9b247088845</v>
-      </c>
-      <c r="BK49" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL49" t="str">
-        <v/>
-      </c>
-      <c r="BM49" t="str">
-        <v/>
-      </c>
-      <c r="BN49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>36745</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C50" t="str">
-        <v>MAC-DONALD</v>
-      </c>
-      <c r="D50" t="str">
-        <v>Renato</v>
-      </c>
-      <c r="E50" t="str">
-        <v>macdonaldrenato4@gmail.com</v>
-      </c>
-      <c r="G50" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H50" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I50" t="str">
-        <v>Vendeur / Vendeuse en accessoires de la personne</v>
-      </c>
-      <c r="L50" t="str">
-        <v>référés Sabah</v>
-      </c>
-      <c r="M50" t="str">
-        <v>2511/novembre 2025 RBX</v>
-      </c>
-      <c r="O50" t="str">
-        <v>SELAM Sabah</v>
-      </c>
-      <c r="P50">
-        <v>20</v>
-      </c>
-      <c r="Q50">
-        <v>19</v>
-      </c>
-      <c r="R50" s="1">
-        <v>38855</v>
-      </c>
-      <c r="S50" t="str">
-        <v>MAC-DONALD</v>
-      </c>
-      <c r="T50" t="str">
-        <v>SAINT-LAURENT DU MARONI, GUYANE FRANÇAISE</v>
-      </c>
-      <c r="U50" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V50" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W50" t="str">
-        <v>12 12 Rue Paul Claudel</v>
-      </c>
-      <c r="X50" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y50" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z50" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA50" t="str">
-        <v>QN05980M</v>
-      </c>
-      <c r="AB50" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC50" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD50" t="str">
-        <v>4 validé</v>
-      </c>
-      <c r="AE50" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF50" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG50" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH50" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI50" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ50" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK50" t="str">
-        <v>379h30m</v>
-      </c>
-      <c r="AL50" t="str">
-        <v>399h</v>
-      </c>
-      <c r="AM50" t="str">
-        <v>117h45m</v>
-      </c>
-      <c r="AN50" s="1">
-        <v>45964</v>
-      </c>
-      <c r="AP50" s="1">
-        <v>46237.083333333336</v>
-      </c>
-      <c r="AV50" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA50" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG50" t="str">
-        <v>597092</v>
-      </c>
-      <c r="BJ50" t="str">
-        <v>c522c80a-5a53-4584-a358-08d638df994e</v>
-      </c>
-      <c r="BK50" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL50" t="str">
-        <v/>
-      </c>
-      <c r="BM50" t="str">
-        <v/>
-      </c>
-      <c r="BN50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>34942</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C51" t="str">
-        <v>ZANANE</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Yasmine</v>
-      </c>
-      <c r="E51" t="str">
-        <v>zanane.yasmine@gmail.com</v>
-      </c>
-      <c r="F51" t="str">
-        <v>0646305979</v>
-      </c>
-      <c r="G51" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="K51" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L51" t="str">
-        <v>référés Sabah</v>
-      </c>
-      <c r="M51" t="str">
-        <v>2509/septembre 2 2025 RBX</v>
-      </c>
-      <c r="O51" t="str">
-        <v>SELAM Sabah</v>
-      </c>
-      <c r="P51">
-        <v>20</v>
-      </c>
-      <c r="Q51">
-        <v>19</v>
-      </c>
-      <c r="R51" s="1">
-        <v>38811</v>
-      </c>
-      <c r="S51" t="str">
-        <v>ZANANE</v>
-      </c>
-      <c r="T51" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="U51" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V51" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W51" t="str">
-        <v>10 10 Avenue du Président Coty Appt 13</v>
-      </c>
-      <c r="X51" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y51" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z51" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA51" t="str">
-        <v>QN05969M</v>
-      </c>
-      <c r="AB51" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC51" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD51" t="str">
-        <v>4 validé</v>
-      </c>
-      <c r="AE51" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF51" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG51" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH51" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI51" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ51" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK51" t="str">
-        <v>447h15m</v>
-      </c>
-      <c r="AL51" t="str">
-        <v>253h15m</v>
-      </c>
-      <c r="AM51" t="str">
-        <v>51h45m</v>
-      </c>
-      <c r="AN51" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO51" s="1">
-        <v>45982.041666666664</v>
-      </c>
-      <c r="AP51" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV51" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA51" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG51" t="str">
-        <v>595602</v>
-      </c>
-      <c r="BJ51" t="str">
-        <v>93bd7ac2-c822-4112-9002-4601fadf0a37</v>
-      </c>
-      <c r="BK51" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL51" t="str">
-        <v/>
-      </c>
-      <c r="BM51" t="str">
-        <v/>
-      </c>
-      <c r="BN51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>34936</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C52" t="str">
-        <v>LE GLATIN</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Kelly</v>
-      </c>
-      <c r="E52" t="str">
-        <v>kellyle2402@gmail.com</v>
-      </c>
-      <c r="F52" t="str">
-        <v>0625609414</v>
-      </c>
-      <c r="G52" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H52" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I52" t="str">
-        <v>Animateur / Animatrice d'accueil collectif de mineurs (ACM), Animateur / Animatrice petite enfance</v>
-      </c>
-      <c r="K52" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L52" t="str">
-        <v>référés Loic</v>
-      </c>
-      <c r="M52" t="str">
-        <v>2509/septembre 2 2025 RBX</v>
-      </c>
-      <c r="O52" t="str">
-        <v>DUCARME Loïc</v>
-      </c>
-      <c r="P52">
-        <v>17</v>
-      </c>
-      <c r="Q52">
-        <v>16</v>
-      </c>
-      <c r="R52" s="1">
-        <v>39868</v>
-      </c>
-      <c r="S52" t="str">
-        <v>Le glatin</v>
-      </c>
-      <c r="T52" t="str">
-        <v>TOURCOING</v>
-      </c>
-      <c r="U52" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V52" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W52" t="str">
-        <v>7 7 Rue Marceau</v>
-      </c>
-      <c r="X52" t="str">
-        <v>59200</v>
-      </c>
-      <c r="Y52" t="str">
-        <v>TOURCOING</v>
-      </c>
-      <c r="Z52" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA52" t="str">
-        <v>QN05983M</v>
-      </c>
-      <c r="AB52" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC52" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD52" t="str">
-        <v>3 non validé</v>
-      </c>
-      <c r="AE52" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF52" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG52" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH52" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI52" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ52" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK52" t="str">
-        <v>299h45m</v>
-      </c>
-      <c r="AL52" t="str">
-        <v>423h30m</v>
-      </c>
-      <c r="AM52" t="str">
-        <v>210h45m</v>
-      </c>
-      <c r="AN52" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO52" s="1">
-        <v>45982.041666666664</v>
-      </c>
-      <c r="AP52" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV52" t="str">
-        <v>MISSION LOCALE DE ROUBAIX</v>
-      </c>
-      <c r="BA52" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG52" t="str">
-        <v>595629</v>
-      </c>
-      <c r="BJ52" t="str">
-        <v>594fb9a9-24d4-4f37-9fc5-9fc25d6e0c30</v>
-      </c>
-      <c r="BK52" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL52" t="str">
-        <v/>
-      </c>
-      <c r="BM52" t="str">
-        <v/>
-      </c>
-      <c r="BN52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>34934</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C53" t="str">
-        <v>BOUKROUH</v>
-      </c>
-      <c r="D53" t="str">
-        <v>Mélina</v>
-      </c>
-      <c r="E53" t="str">
-        <v>melinaboukrouh12@gmail.com</v>
-      </c>
-      <c r="F53" t="str">
-        <v>0746503228</v>
-      </c>
-      <c r="G53" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H53" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I53" t="str">
-        <v>Auxiliaire de gérontologie, Auxiliaire de gériatrie, Auxiliaire de vie, Aide-soignant / Aide-soignante</v>
-      </c>
-      <c r="K53" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L53" t="str">
-        <v>référés Alexia</v>
-      </c>
-      <c r="M53" t="str">
-        <v>2509/septembre 2 2025 RBX</v>
-      </c>
-      <c r="O53" t="str">
-        <v>ARNAUD Alexia</v>
-      </c>
-      <c r="P53">
-        <v>18</v>
-      </c>
-      <c r="Q53">
-        <v>17</v>
-      </c>
-      <c r="R53" s="1">
-        <v>39583</v>
-      </c>
-      <c r="S53" t="str">
-        <v>Boukrouh</v>
-      </c>
-      <c r="T53" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="U53" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V53" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W53" t="str">
-        <v>72 72 Rue du Grand Chemin</v>
-      </c>
-      <c r="X53" t="str">
-        <v>59100</v>
-      </c>
-      <c r="Y53" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="Z53" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA53" t="str">
-        <v>QN05980M</v>
-      </c>
-      <c r="AB53" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC53" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD53" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE53" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF53" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG53" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH53" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI53" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ53" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK53" t="str">
-        <v>291h15m</v>
-      </c>
-      <c r="AL53" t="str">
-        <v>180h</v>
-      </c>
-      <c r="AM53" t="str">
-        <v>178h</v>
-      </c>
-      <c r="AN53" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO53" s="1">
-        <v>45985.041666666664</v>
-      </c>
-      <c r="AP53" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV53" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA53" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG53" t="str">
-        <v>595587</v>
-      </c>
-      <c r="BJ53" t="str">
-        <v>33133dc8-77ac-418d-920d-d103923a6396</v>
-      </c>
-      <c r="BK53" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL53" t="str">
-        <v/>
-      </c>
-      <c r="BM53" t="str">
-        <v/>
-      </c>
-      <c r="BN53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>34933</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C54" t="str">
-        <v>MOLDERS</v>
-      </c>
-      <c r="D54" t="str">
-        <v>Florian</v>
-      </c>
-      <c r="E54" t="str">
-        <v>florianmolders5@gmail.com</v>
-      </c>
-      <c r="F54" t="str">
-        <v>0635821425</v>
-      </c>
-      <c r="G54" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H54" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I54" t="str">
-        <v>Agent / Agente de médiation et de sécurité, Agent / Agente de prévention et de sécurité</v>
-      </c>
-      <c r="K54" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L54" t="str">
-        <v>référés Sabah</v>
-      </c>
-      <c r="M54" t="str">
-        <v>2509/septembre 2 2025 RBX</v>
-      </c>
-      <c r="O54" t="str">
-        <v>SELAM Sabah</v>
-      </c>
-      <c r="P54">
-        <v>22</v>
-      </c>
-      <c r="Q54">
-        <v>21</v>
-      </c>
-      <c r="R54" s="1">
-        <v>38141</v>
-      </c>
-      <c r="S54" t="str">
-        <v>MOLDERS</v>
-      </c>
-      <c r="T54" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="U54" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V54" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W54" t="str">
-        <v>132 132 Rue Nicolas Beaujon</v>
-      </c>
-      <c r="X54" t="str">
-        <v>59510</v>
-      </c>
-      <c r="Y54" t="str">
-        <v>HEM</v>
-      </c>
-      <c r="Z54" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA54" t="str">
-        <v>QN05969M</v>
-      </c>
-      <c r="AB54" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC54" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD54" t="str">
-        <v>4 non validé</v>
-      </c>
-      <c r="AE54" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF54" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG54" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH54" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AI54" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ54" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK54" t="str">
-        <v>360h45m</v>
-      </c>
-      <c r="AL54" t="str">
-        <v>103h</v>
-      </c>
-      <c r="AM54" t="str">
-        <v>167h15m</v>
-      </c>
-      <c r="AN54" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO54" s="1">
-        <v>45982.041666666664</v>
-      </c>
-      <c r="AP54" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV54" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA54" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG54" t="str">
-        <v>595590</v>
-      </c>
-      <c r="BJ54" t="str">
-        <v>b1e00a1e-78d4-4b40-a552-31fc67eb9d50</v>
-      </c>
-      <c r="BK54" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL54" t="str">
-        <v>Formation VRD</v>
-      </c>
-      <c r="BM54" t="str">
-        <v/>
-      </c>
-      <c r="BN54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>32976</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C55" t="str">
-        <v>HABJA ZOUGHAGH</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Amin</v>
-      </c>
-      <c r="E55" t="str">
-        <v>aminhabja8@gmail.com</v>
-      </c>
-      <c r="F55" t="str">
-        <v>0616239774</v>
-      </c>
-      <c r="G55" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H55" t="str">
-        <v>Roubaix</v>
-      </c>
-      <c r="I55" t="str">
-        <v>Carrossier-peintre / Carrossière-peintre</v>
-      </c>
-      <c r="L55" t="str">
-        <v>référés David</v>
-      </c>
-      <c r="M55" t="str">
-        <v>2509/septembre 1 2025</v>
-      </c>
-      <c r="O55" t="str">
-        <v>KIMPE David</v>
-      </c>
-      <c r="P55">
-        <v>19</v>
-      </c>
-      <c r="Q55">
-        <v>18</v>
-      </c>
-      <c r="R55" s="1">
-        <v>39055</v>
-      </c>
-      <c r="S55" t="str">
-        <v>HABJA ZOUGHAGH</v>
-      </c>
-      <c r="T55" t="str">
-        <v>MURCIA, ESPAGNE</v>
-      </c>
-      <c r="U55" t="str">
-        <v>EUROPEENNE</v>
-      </c>
-      <c r="V55" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W55" t="str">
-        <v>5 5 Rue du Caporal Delroeux Appt 12</v>
-      </c>
-      <c r="X55" t="str">
-        <v>59200</v>
-      </c>
-      <c r="Y55" t="str">
-        <v>TOURCOING</v>
-      </c>
-      <c r="Z55" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA55" t="str">
-        <v>QN05985M</v>
-      </c>
-      <c r="AB55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC55" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD55" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG55" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK55" t="str">
-        <v>671h30m</v>
-      </c>
-      <c r="AL55" t="str">
-        <v>606h</v>
-      </c>
-      <c r="AM55" t="str">
-        <v>26h</v>
-      </c>
-      <c r="AN55" s="1">
-        <v>45901</v>
-      </c>
-      <c r="AO55" s="1">
-        <v>45947.083333333336</v>
-      </c>
-      <c r="AP55" s="1">
-        <v>46174.083333333336</v>
-      </c>
-      <c r="AV55" t="str">
-        <v>POLE EMPLOI TOURCOING</v>
-      </c>
-      <c r="AW55" t="str">
-        <v>Zehia BENALI</v>
-      </c>
-      <c r="BA55" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG55" t="str">
-        <v>594253</v>
-      </c>
-      <c r="BJ55" t="str">
-        <v>418fa3e1-9879-4874-8ee3-86f3ae91b2b4</v>
-      </c>
-      <c r="BK55" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL55" t="str">
-        <v/>
-      </c>
-      <c r="BM55" t="str">
-        <v/>
-      </c>
-      <c r="BN55" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BN55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BN40"/>
   </ignoredErrors>
 </worksheet>
 </file>